--- a/exports/466_santa-rosita-de-shirintiari.xlsx
+++ b/exports/466_santa-rosita-de-shirintiari.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M534"/>
+  <dimension ref="A1:M538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24280,113 +24280,109 @@
       <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
+          <t>MOCHI</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>MISHICOLI</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>0</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M381" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr"/>
+      <c r="B382" t="inlineStr">
+        <is>
           <t>MORI</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
+      <c r="C382" t="inlineStr">
         <is>
           <t>AVENCHARI</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr">
+      <c r="D382" t="inlineStr">
         <is>
           <t>RN</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr">
+      <c r="E382" t="inlineStr">
         <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F381" t="n">
+      <c r="F382" t="n">
         <v>4</v>
       </c>
-      <c r="G381" t="inlineStr">
+      <c r="G382" t="inlineStr">
         <is>
           <t>20/01/2022</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr">
+      <c r="H382" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I381" t="inlineStr">
+      <c r="I382" t="inlineStr">
         <is>
           <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
-      <c r="J381" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K381" t="inlineStr">
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
         <is>
           <t>20/01/2023</t>
-        </is>
-      </c>
-      <c r="L381" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M381" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>62000399</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>MORI</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>CAMAYTERI</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>TIMOTEO RIVER</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F382" t="n">
-        <v>21</v>
-      </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>24/04/2005</t>
-        </is>
-      </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>3.JOVEN</t>
-        </is>
-      </c>
-      <c r="I382" t="inlineStr">
-        <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
-        </is>
-      </c>
-      <c r="J382" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K382" t="inlineStr">
-        <is>
-          <t>21/12/2012</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -24401,7 +24397,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>61604380</t>
+          <t>62000399</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -24416,7 +24412,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>RUMI</t>
+          <t>TIMOTEO RIVER</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -24425,11 +24421,11 @@
         </is>
       </c>
       <c r="F383" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>20/12/2007</t>
+          <t>24/04/2005</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -24464,7 +24460,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>62273984</t>
+          <t>61604380</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -24479,25 +24475,25 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>CECILIA</t>
+          <t>RUMI</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F384" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>09/06/2010</t>
+          <t>20/12/2007</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -24527,7 +24523,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>63452734</t>
+          <t>62273984</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -24542,20 +24538,20 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>MISAEL</t>
+          <t>CECILIA</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F385" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>10/02/2013</t>
+          <t>09/06/2010</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -24575,7 +24571,7 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>06/08/2014</t>
+          <t>21/12/2012</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -24590,7 +24586,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>80084338</t>
+          <t>63452734</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -24600,35 +24596,35 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>CAMAYTERI</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>JUANA</t>
+          <t>MISAEL</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F386" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>15/01/1976</t>
+          <t>10/02/2013</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
@@ -24638,7 +24634,7 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>06/08/2014</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -24653,7 +24649,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>80085675</t>
+          <t>80084338</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24668,7 +24664,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>IRMA</t>
+          <t>JUANA</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -24677,11 +24673,11 @@
         </is>
       </c>
       <c r="F387" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>05/04/1978</t>
+          <t>15/01/1976</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24716,7 +24712,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>44708509</t>
+          <t>80085675</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -24731,20 +24727,20 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>ARMANDO</t>
+          <t>IRMA</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F388" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>09/09/1984</t>
+          <t>05/04/1978</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -24764,7 +24760,7 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>21/12/2012</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -24779,7 +24775,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>45183606</t>
+          <t>44708509</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -24794,7 +24790,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>ARMANDO</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -24803,11 +24799,11 @@
         </is>
       </c>
       <c r="F389" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>03/04/1985</t>
+          <t>09/09/1984</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -24827,7 +24823,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>21/12/2012</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -24842,35 +24838,35 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>61737452</t>
+          <t>45183606</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>NAPO</t>
+          <t>MORI</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>VELA</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>NATALIA</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F390" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>08/08/1996</t>
+          <t>03/04/1985</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24890,7 +24886,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>01/06/2015</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -24905,22 +24901,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>94076107</t>
+          <t>61737452</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>NAPO</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>ASHISHO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>KEYSSI AYTANA</t>
+          <t>NATALIA</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -24929,21 +24925,21 @@
         </is>
       </c>
       <c r="F391" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>10/12/2024</t>
+          <t>08/08/1996</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
@@ -24953,7 +24949,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>01/06/2015</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -24968,7 +24964,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>82164062</t>
+          <t>94076107</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -24978,12 +24974,12 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>CRISTOBAL</t>
+          <t>ASHISHO</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>THASHA ARIANA</t>
+          <t>KEYSSI AYTANA</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -24992,11 +24988,11 @@
         </is>
       </c>
       <c r="F392" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>25/11/2023</t>
+          <t>10/12/2024</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25016,7 +25012,7 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -25031,7 +25027,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>72611782</t>
+          <t>82164062</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25041,12 +25037,12 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>CRISTOBAL</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>LUCY IVETT</t>
+          <t>THASHA ARIANA</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -25055,21 +25051,21 @@
         </is>
       </c>
       <c r="F393" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>09/12/1994</t>
+          <t>25/11/2023</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -25079,7 +25075,7 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>10/11/2011</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -25094,7 +25090,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>93754592</t>
+          <t>72611782</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25104,12 +25100,12 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>SUNI ARELY</t>
+          <t>LUCY IVETT</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -25118,21 +25114,21 @@
         </is>
       </c>
       <c r="F394" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>25/02/2024</t>
+          <t>09/12/1994</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
@@ -25142,7 +25138,7 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>10/11/2011</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -25157,22 +25153,22 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>72291251</t>
+          <t>72611784</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>OMPIQUIRI</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>ADARMES</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>BERLY</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -25181,16 +25177,16 @@
         </is>
       </c>
       <c r="F395" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>07/04/1991</t>
+          <t>11/09/1997</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -25205,7 +25201,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -25220,22 +25216,22 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>20980081</t>
+          <t>93754592</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>OMPIQUIRI</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>CASHANTIOTE</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>CESARINA</t>
+          <t>SUNI ARELY</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -25244,21 +25240,21 @@
         </is>
       </c>
       <c r="F396" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>07/10/1938</t>
+          <t>25/02/2024</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
@@ -25268,7 +25264,7 @@
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>06/04/2015</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -25283,22 +25279,22 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>20086251</t>
+          <t>72291251</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>ONICA</t>
+          <t>OMPIQUIRI</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>ADARMES</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>ROGELIO</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -25307,11 +25303,11 @@
         </is>
       </c>
       <c r="F397" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>01/03/1974</t>
+          <t>07/04/1991</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -25321,7 +25317,7 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -25331,7 +25327,7 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -25346,45 +25342,45 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>76989075</t>
+          <t>20980081</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>ONICA</t>
+          <t>OMPIQUIRI</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>CASHANTIOTE</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>ALEXANDER</t>
+          <t>CESARINA</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>09/12/1997</t>
+          <t>07/10/1938</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
@@ -25394,7 +25390,7 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>06/04/2015</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -25409,7 +25405,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>61551258</t>
+          <t>20086251</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -25419,35 +25415,35 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>MARI CARMEN</t>
+          <t>ROGELIO</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>02/12/2000</t>
+          <t>01/03/1974</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -25472,7 +25468,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>61551259</t>
+          <t>76989075</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -25487,7 +25483,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>ELMER ROGELIO</t>
+          <t>ALEXANDER</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -25496,11 +25492,11 @@
         </is>
       </c>
       <c r="F400" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>05/04/2004</t>
+          <t>09/12/1997</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -25510,7 +25506,7 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
@@ -25535,7 +25531,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>60401496</t>
+          <t>61551258</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -25550,7 +25546,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>LIUZ DELIA</t>
+          <t>MARI CARMEN</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -25559,11 +25555,11 @@
         </is>
       </c>
       <c r="F401" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>25/11/2008</t>
+          <t>02/12/2000</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -25598,7 +25594,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>81183663</t>
+          <t>61551259</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -25608,35 +25604,35 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>KAMAITERI</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>EVELYN SANYURI</t>
+          <t>ELMER ROGELIO</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F402" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>07/10/2014</t>
+          <t>05/04/2004</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -25646,7 +25642,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>09/06/2015</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -25661,7 +25657,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>81808338</t>
+          <t>60401496</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -25671,35 +25667,35 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>WILIAM ALFREDO</t>
+          <t>LIUZ DELIA</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F403" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>13/09/2018</t>
+          <t>25/11/2008</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -25709,7 +25705,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>13/09/2023</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -25724,7 +25720,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>82003245</t>
+          <t>81183663</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -25734,12 +25730,12 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>KAMAITERI</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>JHUMI SAHIRED</t>
+          <t>EVELYN SANYURI</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -25748,21 +25744,21 @@
         </is>
       </c>
       <c r="F404" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>04/05/2023</t>
+          <t>07/10/2014</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -25772,7 +25768,7 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>01/09/2023</t>
+          <t>09/06/2015</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -25787,22 +25783,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>94212779</t>
+          <t>81808338</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>ONICA</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>YOSHIRO BONIFACIO</t>
+          <t>WILIAM ALFREDO</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -25811,11 +25807,11 @@
         </is>
       </c>
       <c r="F405" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>08/04/2025</t>
+          <t>13/09/2018</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -25825,7 +25821,7 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -25835,7 +25831,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>13/09/2023</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -25850,22 +25846,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>44708511</t>
+          <t>82003245</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>ONICA</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>ALEJANDRINA</t>
+          <t>JHUMI SAHIRED</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -25874,21 +25870,21 @@
         </is>
       </c>
       <c r="F406" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>24/06/1981</t>
+          <t>04/05/2023</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
@@ -25898,7 +25894,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>01/09/2023</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -25913,45 +25909,45 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>46442728</t>
+          <t>94212779</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>MARCELINA</t>
+          <t>YOSHIRO BONIFACIO</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F407" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>21/01/1984</t>
+          <t>08/04/2025</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
@@ -25961,7 +25957,7 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -25976,7 +25972,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>74422358</t>
+          <t>44708511</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -25991,7 +25987,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>LUCILA</t>
+          <t>ALEJANDRINA</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -26000,16 +25996,16 @@
         </is>
       </c>
       <c r="F408" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>17/12/1998</t>
+          <t>24/06/1981</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -26024,7 +26020,7 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
@@ -26039,7 +26035,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>21009888</t>
+          <t>46442728</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26049,30 +26045,30 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>ABRAN</t>
+          <t>MARCELINA</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>15/08/1964</t>
+          <t>21/01/1984</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -26102,35 +26098,35 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>60300885</t>
+          <t>74422358</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>PEGO</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>JENNER LUIS</t>
+          <t>LUCILA</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>28/12/2006</t>
+          <t>17/12/1998</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26140,7 +26136,7 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -26150,7 +26146,7 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -26165,40 +26161,40 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>62690625</t>
+          <t>21009888</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>PEGO</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>LLEYSIN MARICTZA</t>
+          <t>ABRAN</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>26/05/2013</t>
+          <t>15/08/1964</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -26213,7 +26209,7 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>09/06/2015</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -26228,7 +26224,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>80421430</t>
+          <t>60300885</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -26238,12 +26234,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>CESAR</t>
+          <t>JENNER LUIS</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -26252,21 +26248,21 @@
         </is>
       </c>
       <c r="F412" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>09/11/1979</t>
+          <t>28/12/2006</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
@@ -26291,22 +26287,22 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>81872647</t>
+          <t>62690625</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>PERALTA</t>
+          <t>PEGO</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>BLANCO</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>FELICIA LINDA</t>
+          <t>LLEYSIN MARICTZA</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -26315,21 +26311,21 @@
         </is>
       </c>
       <c r="F413" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>15/02/2021</t>
+          <t>26/05/2013</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -26339,7 +26335,7 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>09/06/2015</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
@@ -26354,40 +26350,40 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>62809060</t>
+          <t>80421430</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>PEZO</t>
+          <t>PEGO</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>CAMINTI</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>ELITA</t>
+          <t>CESAR</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>12/09/2001</t>
+          <t>09/11/1979</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -26402,7 +26398,7 @@
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>08/05/2012</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
@@ -26417,22 +26413,22 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>48562212</t>
+          <t>81872647</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>PINHO</t>
+          <t>PERALTA</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>BLANCO</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>VERONICA ANGELICA</t>
+          <t>FELICIA LINDA</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -26441,21 +26437,21 @@
         </is>
       </c>
       <c r="F415" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>25/05/1988</t>
+          <t>15/02/2021</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -26465,7 +26461,7 @@
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>17/11/2012</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
@@ -26480,45 +26476,45 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>82003212</t>
+          <t>62809060</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>PIROCO</t>
+          <t>PEZO</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>KAMAITERI</t>
+          <t>CAMINTI</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>PABLO</t>
+          <t>ELITA</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>30/05/2022</t>
+          <t>12/09/2001</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -26528,7 +26524,7 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>07/01/2023</t>
+          <t>08/05/2012</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
@@ -26543,22 +26539,22 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>82369305</t>
+          <t>48562212</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>PLASHICO</t>
+          <t>PINHO</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>MISHICOLI</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>ARLETH ANALI BETH</t>
+          <t>VERONICA ANGELICA</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -26567,21 +26563,21 @@
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>25/05/1988</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
@@ -26591,7 +26587,7 @@
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>27/05/2024</t>
+          <t>17/11/2012</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -26606,45 +26602,45 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>62274147</t>
+          <t>82003212</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>PIROCO</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>KAMAITERI</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>ROSSY BELL</t>
+          <t>PABLO</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>14/08/2012</t>
+          <t>30/05/2022</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -26654,7 +26650,7 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>07/01/2023</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -26669,22 +26665,22 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>93857741</t>
+          <t>82369305</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>PRADO</t>
+          <t>PLASHICO</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>LUCRECIA</t>
+          <t>MISHICOLI</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>KEYMI SHIOMY</t>
+          <t>ARLETH ANALI BETH</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -26693,11 +26689,11 @@
         </is>
       </c>
       <c r="F419" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>02/06/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -26717,7 +26713,7 @@
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>27/05/2024</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
@@ -26732,22 +26728,22 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>80085596</t>
+          <t>62274147</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>QUENTIMARI</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>MARIANO</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>GLORIA</t>
+          <t>ROSSY BELL</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -26756,21 +26752,21 @@
         </is>
       </c>
       <c r="F420" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>13/04/1979</t>
+          <t>14/08/2012</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
@@ -26780,7 +26776,7 @@
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
@@ -26795,35 +26791,35 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>81971708</t>
+          <t>93857741</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>QUENTISHA</t>
+          <t>PRADO</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>LUCRECIA</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>LANFAN TABALU</t>
+          <t>KEYMI SHIOMY</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F421" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>02/11/2023</t>
+          <t>02/06/2024</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -26843,7 +26839,7 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>22/07/2024</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -26858,35 +26854,35 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>60401473</t>
+          <t>80085596</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>QUENTIMARI</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>AMPATI</t>
+          <t>MARIANO</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>CRISTIAN</t>
+          <t>GLORIA</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>03/05/1995</t>
+          <t>13/04/1979</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -26921,22 +26917,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>60300853</t>
+          <t>81971708</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>QUENTISHA</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>AMPATI</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>EFRAIN</t>
+          <t>LANFAN TABALU</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -26945,21 +26941,21 @@
         </is>
       </c>
       <c r="F423" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>14/04/2007</t>
+          <t>02/11/2023</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -26969,7 +26965,7 @@
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>22/07/2024</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
@@ -26984,7 +26980,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>21009964</t>
+          <t>60401473</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -26994,12 +26990,12 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>AMPATI</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>TEOFILO</t>
+          <t>CRISTIAN</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -27008,11 +27004,11 @@
         </is>
       </c>
       <c r="F424" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>05/01/1969</t>
+          <t>03/05/1995</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -27047,7 +27043,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>21009957</t>
+          <t>60300853</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -27057,35 +27053,35 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>AMPATI</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>IRENE</t>
+          <t>EFRAIN</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F425" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>08/08/1972</t>
+          <t>14/04/2007</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -27095,7 +27091,7 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>30/10/2012</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
@@ -27110,7 +27106,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>81808325</t>
+          <t>21009964</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -27120,12 +27116,12 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>DIQUES</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>YELSIN GABRIEL</t>
+          <t>TEOFILO</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -27134,16 +27130,16 @@
         </is>
       </c>
       <c r="F426" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>16/02/2018</t>
+          <t>05/01/1969</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -27158,7 +27154,7 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>16/02/2023</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -27173,7 +27169,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>82369324</t>
+          <t>21009957</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -27183,12 +27179,12 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>SHINA</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>KEYLI JULIET</t>
+          <t>IRENE</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -27197,21 +27193,21 @@
         </is>
       </c>
       <c r="F427" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>13/02/2024</t>
+          <t>08/08/1972</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -27221,7 +27217,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>27/05/2024</t>
+          <t>30/10/2012</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -27236,35 +27232,35 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>81808102</t>
+          <t>81808325</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>VALDERRAMA</t>
+          <t>DIQUES</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>LYA MERCEDEZ</t>
+          <t>YELSIN GABRIEL</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>22/07/2015</t>
+          <t>16/02/2018</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -27274,7 +27270,7 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -27284,7 +27280,7 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>12/09/2020</t>
+          <t>16/02/2023</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -27299,45 +27295,45 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>80717362</t>
+          <t>82369324</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>RATTERI</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>SHINA</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>JUAN PABLO</t>
+          <t>KEYLI JULIET</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>04/03/2005</t>
+          <t>13/02/2024</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
@@ -27347,7 +27343,7 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>21/02/2022</t>
+          <t>27/05/2024</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -27362,45 +27358,45 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>77698244</t>
+          <t>81808102</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>RATTERI</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>VALDERRAMA</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>PIERO LUIGI</t>
+          <t>LYA MERCEDEZ</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>18/08/2005</t>
+          <t>22/07/2015</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
@@ -27410,7 +27406,7 @@
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>29/10/2012</t>
+          <t>12/09/2020</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
@@ -27425,7 +27421,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>00150663</t>
+          <t>80717362</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -27435,12 +27431,12 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>LUIS ANGEL</t>
+          <t>JUAN PABLO</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -27449,16 +27445,16 @@
         </is>
       </c>
       <c r="F431" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>06/02/1955</t>
+          <t>04/03/2005</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -27473,7 +27469,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>29/10/2012</t>
+          <t>21/02/2022</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -27488,45 +27484,45 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>81183723</t>
+          <t>77698244</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>RATTERI</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>KATTERINE MIRIELA</t>
+          <t>PIERO LUIGI</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>13/06/2015</t>
+          <t>18/08/2005</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
@@ -27536,7 +27532,7 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>12/09/2020</t>
+          <t>29/10/2012</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -27551,35 +27547,35 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>20086279</t>
+          <t>00150663</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>REATEGUI</t>
+          <t>RATTERI</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>MARLENI</t>
+          <t>LUIS ANGEL</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>05/07/1965</t>
+          <t>06/02/1955</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -27599,7 +27595,7 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>29/10/2012</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
@@ -27614,45 +27610,45 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>44712764</t>
+          <t>81183723</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>REATEGUI</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>SAMANCHAQUI</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>FAUSTO</t>
+          <t>KATTERINE MIRIELA</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>22/06/1959</t>
+          <t>13/06/2015</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -27662,7 +27658,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>12/09/2020</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
@@ -27677,22 +27673,22 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>63191364</t>
+          <t>20086279</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>REATEGUI</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>MARLENI</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -27701,16 +27697,16 @@
         </is>
       </c>
       <c r="F435" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>13/02/2003</t>
+          <t>05/07/1965</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27725,7 +27721,7 @@
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>02/03/2015</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
@@ -27740,22 +27736,22 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>93747405</t>
+          <t>44712764</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>REATEGUI</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>MELCHOR</t>
+          <t>SAMANCHAQUI</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>DYLAN JHARED EDUARDO</t>
+          <t>FAUSTO</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -27764,21 +27760,21 @@
         </is>
       </c>
       <c r="F436" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>22/06/1959</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -27788,7 +27784,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
@@ -27803,22 +27799,22 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>73979687</t>
+          <t>63191364</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>HERMILA</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -27827,21 +27823,21 @@
         </is>
       </c>
       <c r="F437" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>16/05/1995</t>
+          <t>13/02/2003</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -27851,7 +27847,7 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>02/03/2015</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
@@ -27864,29 +27860,25 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>94620099</t>
-        </is>
-      </c>
+      <c r="A438" t="inlineStr"/>
       <c r="B438" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>REVILLA</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>KAEL LEIN FRAIN</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F438" t="n">
@@ -27894,7 +27886,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27914,7 +27906,7 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
@@ -27927,37 +27919,33 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>92093102</t>
-        </is>
-      </c>
+      <c r="A439" t="inlineStr"/>
       <c r="B439" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>AZENETH</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F439" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>03/11/2020</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27967,7 +27955,7 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -27977,7 +27965,7 @@
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -27992,22 +27980,22 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>23693751</t>
+          <t>93747405</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>MELCHOR</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>TEODORO</t>
+          <t>DYLAN JHARED EDUARDO</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -28016,21 +28004,21 @@
         </is>
       </c>
       <c r="F440" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>19/09/1974</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -28040,7 +28028,7 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -28055,22 +28043,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>93334714</t>
+          <t>73979687</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>RUFINO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>ASENETH SHANIN</t>
+          <t>HERMILA</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -28079,21 +28067,21 @@
         </is>
       </c>
       <c r="F441" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>06/04/2023</t>
+          <t>16/05/1995</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -28103,7 +28091,7 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>17/04/2024</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -28118,45 +28106,45 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>62000412</t>
+          <t>94620099</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>REVILLA</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>BETMA</t>
+          <t>KAEL LEIN FRAIN</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F442" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>21/04/2004</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -28166,7 +28154,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>18/10/2011</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -28181,22 +28169,22 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>21009889</t>
+          <t>92093102</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>TEREZA</t>
+          <t>AZENETH</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -28205,21 +28193,21 @@
         </is>
       </c>
       <c r="F443" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>18/05/1958</t>
+          <t>03/11/2020</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
@@ -28229,7 +28217,7 @@
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>18/10/2011</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
@@ -28244,35 +28232,35 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>71088552</t>
+          <t>23693751</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>CLISENCIA</t>
+          <t>TEODORO</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F444" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>29/07/1995</t>
+          <t>19/09/1974</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -28282,7 +28270,7 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
@@ -28292,7 +28280,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
@@ -28307,45 +28295,45 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>80084333</t>
+          <t>93334714</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RUFINO</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>ASENETH SHANIN</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F445" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>25/06/1971</t>
+          <t>06/04/2023</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
@@ -28355,7 +28343,7 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
@@ -28368,43 +28356,47 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr"/>
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>62000412</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>BETMA</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>13/09/2023</t>
+          <t>21/04/2004</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -28414,7 +28406,7 @@
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>13/09/2023</t>
+          <t>18/10/2011</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -28429,45 +28421,45 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>62273993</t>
+          <t>21009889</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>OSWALDO</t>
+          <t>TEREZA</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>07/10/1996</t>
+          <t>18/05/1958</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -28477,7 +28469,7 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>18/10/2011</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
@@ -28492,22 +28484,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>77802065</t>
+          <t>71088552</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>VALERIA DEYSI</t>
+          <t>CLISENCIA</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -28516,16 +28508,16 @@
         </is>
       </c>
       <c r="F448" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>21/06/2001</t>
+          <t>29/07/1995</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -28540,7 +28532,7 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
@@ -28555,7 +28547,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>77802064</t>
+          <t>80084333</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -28565,35 +28557,35 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>VILCIA</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>14/09/2002</t>
+          <t>25/06/1971</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
@@ -28616,11 +28608,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>61604357</t>
-        </is>
-      </c>
+      <c r="A450" t="inlineStr"/>
       <c r="B450" t="inlineStr">
         <is>
           <t>SANCHEZ</t>
@@ -28628,12 +28616,12 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>JHONI CLEVER</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -28642,21 +28630,21 @@
         </is>
       </c>
       <c r="F450" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>19/12/2006</t>
+          <t>13/09/2023</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
@@ -28666,7 +28654,7 @@
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>13/09/2023</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
@@ -28681,7 +28669,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>61604358</t>
+          <t>62273993</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -28696,7 +28684,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>CLIVER</t>
+          <t>OSWALDO</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -28705,16 +28693,16 @@
         </is>
       </c>
       <c r="F451" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>14/12/2008</t>
+          <t>07/10/1996</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28744,7 +28732,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>63452742</t>
+          <t>77802065</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -28754,35 +28742,35 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>GARLIA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>MAYNER</t>
+          <t>VALERIA DEYSI</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>21/11/2012</t>
+          <t>21/06/2001</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -28792,7 +28780,7 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>06/08/2014</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -28807,7 +28795,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>63452761</t>
+          <t>77802064</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -28817,12 +28805,12 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>GARLIA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>ELIANA</t>
+          <t>VILCIA</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -28831,21 +28819,21 @@
         </is>
       </c>
       <c r="F453" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>28/01/2014</t>
+          <t>14/09/2002</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -28855,7 +28843,7 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>20/10/2014</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -28870,7 +28858,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>80839080</t>
+          <t>61604357</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -28880,35 +28868,35 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>KEYSI CELINA</t>
+          <t>JHONI CLEVER</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>17/01/2014</t>
+          <t>19/12/2006</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -28918,7 +28906,7 @@
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>30/03/2016</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
@@ -28933,7 +28921,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>81367664</t>
+          <t>61604358</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -28943,12 +28931,12 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>RALY</t>
+          <t>CLIVER</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -28957,21 +28945,21 @@
         </is>
       </c>
       <c r="F455" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>25/12/2015</t>
+          <t>14/12/2008</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -28981,7 +28969,7 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>30/12/2020</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
@@ -28996,7 +28984,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>81808133</t>
+          <t>63452742</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -29006,12 +28994,12 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>GARLIA</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>YAYR</t>
+          <t>MAYNER</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -29020,21 +29008,21 @@
         </is>
       </c>
       <c r="F456" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>21/01/2019</t>
+          <t>21/11/2012</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -29044,7 +29032,7 @@
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>21/01/2024</t>
+          <t>06/08/2014</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -29059,7 +29047,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>82003232</t>
+          <t>63452761</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -29069,12 +29057,12 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>GARLIA</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>KATIA NICOL</t>
+          <t>ELIANA</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -29083,21 +29071,21 @@
         </is>
       </c>
       <c r="F457" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>31/01/2023</t>
+          <t>28/01/2014</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -29107,7 +29095,7 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>05/06/2023</t>
+          <t>20/10/2014</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -29122,7 +29110,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>63452862</t>
+          <t>80839080</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -29132,30 +29120,30 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>PANDURO</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>PAUL ALY</t>
+          <t>KEYSI CELINA</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F458" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>25/09/2017</t>
+          <t>17/01/2014</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -29170,7 +29158,7 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>25/09/2022</t>
+          <t>30/03/2016</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -29185,7 +29173,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>72575052</t>
+          <t>81367664</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -29195,12 +29183,12 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>IDELSON</t>
+          <t>RALY</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -29209,16 +29197,16 @@
         </is>
       </c>
       <c r="F459" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>21/04/1994</t>
+          <t>25/12/2015</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -29233,7 +29221,7 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>30/12/2020</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
@@ -29246,7 +29234,11 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr"/>
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>81808133</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>SANCHEZ</t>
@@ -29254,25 +29246,25 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>YAYR</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>19/05/2024</t>
+          <t>21/01/2019</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -29282,7 +29274,7 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -29292,7 +29284,7 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>19/05/2024</t>
+          <t>21/01/2024</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -29307,27 +29299,27 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>82202905</t>
+          <t>82003232</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>SANCHO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>CRISTIAN</t>
+          <t>KATIA NICOL</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F461" t="n">
@@ -29335,7 +29327,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>12/02/2023</t>
+          <t>31/01/2023</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -29355,7 +29347,7 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>05/06/2023</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
@@ -29370,22 +29362,22 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>20086242</t>
+          <t>63452862</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>MISCAY</t>
+          <t>PANDURO</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>PAUL ALY</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -29394,16 +29386,16 @@
         </is>
       </c>
       <c r="F462" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>05/04/1971</t>
+          <t>25/09/2017</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -29418,7 +29410,7 @@
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>25/09/2022</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -29433,108 +29425,104 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>47477397</t>
+          <t>72575052</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>MISHICOLI</t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>MELITA</t>
+          <t>IDELSON</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F463" t="n">
+        <v>32</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>21/04/1994</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>19/12/2012</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M463" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr"/>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>VARGAS</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F463" t="n">
-        <v>35</v>
-      </c>
-      <c r="G463" t="inlineStr">
-        <is>
-          <t>25/10/1991</t>
-        </is>
-      </c>
-      <c r="H463" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I463" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J463" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K463" t="inlineStr">
-        <is>
-          <t>19/12/2012</t>
-        </is>
-      </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M463" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>62273934</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>SANTIAGO</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>MISHICOLI</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>PERCY</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
       <c r="F464" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>22/07/2006</t>
+          <t>19/05/2024</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -29544,7 +29532,7 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>19/05/2024</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
@@ -29559,45 +29547,45 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>63346015</t>
+          <t>82202905</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>SANCHO</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>MISHICOLI</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>LUZ MARIA</t>
+          <t>CRISTIAN</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F465" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>22/09/2006</t>
+          <t>12/02/2023</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
@@ -29607,7 +29595,7 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -29622,22 +29610,22 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>81932630</t>
+          <t>20086242</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>SHEVANCORI</t>
+          <t>MISCAY</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>RIMI</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -29646,21 +29634,21 @@
         </is>
       </c>
       <c r="F466" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>02/05/2021</t>
+          <t>05/04/1971</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
@@ -29670,7 +29658,7 @@
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
@@ -29685,45 +29673,45 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>72603687</t>
+          <t>47477397</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>SEBERIANO</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>MISHICOLI</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>ELIO</t>
+          <t>MELITA</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F467" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>12/07/1998</t>
+          <t>25/10/1991</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -29733,7 +29721,7 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -29748,22 +29736,22 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>80084344</t>
+          <t>62273934</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>SEBERIANO</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MISHICOLI</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>BENANCIO</t>
+          <t>PERCY</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -29772,21 +29760,21 @@
         </is>
       </c>
       <c r="F468" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>06/06/1976</t>
+          <t>22/07/2006</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -29796,7 +29784,7 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
@@ -29811,22 +29799,22 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>48847636</t>
+          <t>63346015</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>SEBERIANO</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MISHICOLI</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>MERLY</t>
+          <t>LUZ MARIA</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -29835,21 +29823,21 @@
         </is>
       </c>
       <c r="F469" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>30/04/1985</t>
+          <t>22/09/2006</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -29859,7 +29847,7 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>05/02/2015</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
@@ -29874,45 +29862,45 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>20086273</t>
+          <t>81932630</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>SEMERI</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>SHEVANCORI</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>DORITA</t>
+          <t>RIMI</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F470" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>26/01/1956</t>
+          <t>02/05/2021</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -29922,7 +29910,7 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -29937,45 +29925,45 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>20086276</t>
+          <t>72603687</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>SEBERIANO</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>CHOMPATI</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>CAROLA</t>
+          <t>ELIO</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F471" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>09/02/1968</t>
+          <t>12/07/1998</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
@@ -29985,7 +29973,7 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>06/02/2015</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
@@ -30000,22 +29988,22 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>80430197</t>
+          <t>80084344</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>SEBERIANO</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>USIAS</t>
+          <t>BENANCIO</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -30024,11 +30012,11 @@
         </is>
       </c>
       <c r="F472" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>09/01/1977</t>
+          <t>06/06/1976</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -30038,7 +30026,7 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
@@ -30048,7 +30036,7 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>03/05/2024</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
@@ -30063,22 +30051,22 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>20086165</t>
+          <t>48847636</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>SEBERIANO</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>YERNON</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>RAQUEL</t>
+          <t>MERLY</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -30087,11 +30075,11 @@
         </is>
       </c>
       <c r="F473" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>21/09/1976</t>
+          <t>30/04/1985</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -30111,7 +30099,7 @@
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>27/03/2018</t>
+          <t>05/02/2015</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -30126,22 +30114,22 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>43223633</t>
+          <t>20086273</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>SHABONTI</t>
+          <t>SEMERI</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>LILA</t>
+          <t>DORITA</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -30150,21 +30138,21 @@
         </is>
       </c>
       <c r="F474" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>09/05/1982</t>
+          <t>26/01/1956</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
@@ -30174,7 +30162,7 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>29/10/2012</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
@@ -30189,45 +30177,45 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>72603683</t>
+          <t>20086276</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>SHAVONTI</t>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>CHOMPATI</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>JACKIMER</t>
+          <t>CAROLA</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>26/10/2001</t>
+          <t>09/02/1968</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
@@ -30237,7 +30225,7 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>06/02/2015</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
@@ -30252,45 +30240,45 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>72603685</t>
+          <t>80430197</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>SHAVONTI</t>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>NAY</t>
+          <t>USIAS</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>22/06/2003</t>
+          <t>09/01/1977</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
@@ -30300,7 +30288,7 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>03/05/2024</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -30315,45 +30303,45 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>61604385</t>
+          <t>20086165</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>SHAVONTI</t>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>YERNON</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>RAQUEL</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>28/12/2008</t>
+          <t>21/09/1976</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
@@ -30363,7 +30351,7 @@
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>27/03/2018</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
@@ -30378,45 +30366,45 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>63452741</t>
+          <t>43223633</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>SHAVONTI</t>
+          <t>SHABONTI</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>EDGAR</t>
+          <t>LILA</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>03/03/2013</t>
+          <t>09/05/1982</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
@@ -30426,7 +30414,7 @@
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>06/08/2014</t>
+          <t>29/10/2012</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
@@ -30441,7 +30429,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>80085672</t>
+          <t>72603683</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -30451,12 +30439,12 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>HASA</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>PACION</t>
+          <t>JACKIMER</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -30465,21 +30453,21 @@
         </is>
       </c>
       <c r="F479" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>09/04/1976</t>
+          <t>26/10/2001</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
@@ -30489,7 +30477,7 @@
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
@@ -30504,7 +30492,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>80085665</t>
+          <t>72603685</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -30514,35 +30502,35 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>HASA</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>NAY</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>07/09/1978</t>
+          <t>22/06/2003</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
@@ -30552,7 +30540,7 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -30567,7 +30555,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>44590209</t>
+          <t>61604385</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -30577,12 +30565,12 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>HASA</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>PANCHO</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -30591,21 +30579,21 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>09/04/1981</t>
+          <t>28/12/2008</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
@@ -30630,7 +30618,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>60401552</t>
+          <t>63452741</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -30640,12 +30628,12 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>HIVI</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>EDER ROY</t>
+          <t>EDGAR</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -30654,16 +30642,16 @@
         </is>
       </c>
       <c r="F482" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>22/07/2002</t>
+          <t>03/03/2013</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -30678,7 +30666,7 @@
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>06/08/2014</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -30693,7 +30681,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>60401551</t>
+          <t>80085672</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -30703,35 +30691,35 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>HIVI</t>
+          <t>HASA</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>ANALIBETH</t>
+          <t>PACION</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F483" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>26/03/2008</t>
+          <t>09/04/1976</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -30756,7 +30744,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>74413369</t>
+          <t>80085665</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -30766,12 +30754,12 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>IVI</t>
+          <t>HASA</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t>IVAN</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -30780,11 +30768,11 @@
         </is>
       </c>
       <c r="F484" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>08/06/1996</t>
+          <t>07/09/1978</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -30794,7 +30782,7 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -30804,7 +30792,7 @@
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
@@ -30819,7 +30807,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>74413370</t>
+          <t>44590209</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -30829,12 +30817,12 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>IVI</t>
+          <t>HASA</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>LINO</t>
+          <t>PANCHO</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -30843,16 +30831,16 @@
         </is>
       </c>
       <c r="F485" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>02/05/1998</t>
+          <t>09/04/1981</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30867,7 +30855,7 @@
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
@@ -30882,7 +30870,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>62000372</t>
+          <t>60401552</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -30892,25 +30880,25 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>IVI</t>
+          <t>HIVI</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>LESLI PILAR</t>
+          <t>EDER ROY</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F486" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>22/08/2003</t>
+          <t>22/07/2002</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -30920,7 +30908,7 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
@@ -30945,7 +30933,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>74805409</t>
+          <t>60401551</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -30955,25 +30943,25 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>IVI</t>
+          <t>HIVI</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>CARLOS TARCICIO</t>
+          <t>ANALIBETH</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F487" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>02/01/2006</t>
+          <t>26/03/2008</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -31008,7 +30996,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>72575135</t>
+          <t>74413369</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -31018,12 +31006,12 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>QUENTIMARI</t>
+          <t>IVI</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>HIMER</t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -31032,21 +31020,21 @@
         </is>
       </c>
       <c r="F488" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>30/12/2000</t>
+          <t>08/06/1996</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
@@ -31056,7 +31044,7 @@
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
@@ -31071,7 +31059,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>60289798</t>
+          <t>74413370</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -31081,12 +31069,12 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>QUENTIMARI</t>
+          <t>IVI</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>WALTER WALDIR</t>
+          <t>LINO</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -31095,11 +31083,11 @@
         </is>
       </c>
       <c r="F489" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>25/03/2007</t>
+          <t>02/05/1998</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -31109,7 +31097,7 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
@@ -31119,7 +31107,7 @@
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -31134,7 +31122,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>63452719</t>
+          <t>62000372</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -31144,12 +31132,12 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>QUENTIMARI</t>
+          <t>IVI</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>ZANDY XIOMARA</t>
+          <t>LESLI PILAR</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -31158,21 +31146,21 @@
         </is>
       </c>
       <c r="F490" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>13/06/2012</t>
+          <t>22/08/2003</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
@@ -31182,7 +31170,7 @@
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>07/05/2014</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
@@ -31197,22 +31185,22 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>60401479</t>
+          <t>74805409</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>SHINA</t>
+          <t>SHAVONTI</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>IVI</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>YIMI ERNESTO</t>
+          <t>CARLOS TARCICIO</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -31221,11 +31209,11 @@
         </is>
       </c>
       <c r="F491" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>03/11/2003</t>
+          <t>02/01/2006</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -31245,7 +31233,7 @@
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>29/10/2012</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
@@ -31260,40 +31248,40 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>62184617</t>
+          <t>72575135</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>SHINA</t>
+          <t>SHAVONTI</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>QUENTIMARI</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>ROCIO DEL PILAR</t>
+          <t>HIMER</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>02/04/2009</t>
+          <t>30/12/2000</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -31308,7 +31296,7 @@
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>29/10/2012</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -31323,22 +31311,22 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>81808123</t>
+          <t>60289798</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>SHINA</t>
+          <t>SHAVONTI</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>QUENTIMARI</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>GILBERTO GABRIEL</t>
+          <t>WALTER WALDIR</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -31347,21 +31335,21 @@
         </is>
       </c>
       <c r="F493" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>28/03/2018</t>
+          <t>25/03/2007</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
@@ -31371,7 +31359,7 @@
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>28/03/2023</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -31386,45 +31374,45 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>80421441</t>
+          <t>63452719</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>SITICONANTSI</t>
+          <t>SHAVONTI</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>AMPATI</t>
+          <t>QUENTIMARI</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>LEONARDO</t>
+          <t>ZANDY XIOMARA</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>02/01/1979</t>
+          <t>13/06/2012</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
@@ -31434,7 +31422,7 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>07/05/2014</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -31449,40 +31437,40 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>60103167</t>
+          <t>62184617</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>SITICONANTSI</t>
+          <t>SHINA</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>YONER</t>
+          <t>ROCIO DEL PILAR</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>06/12/2000</t>
+          <t>02/04/2009</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -31497,7 +31485,7 @@
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>29/10/2012</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -31512,114 +31500,118 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>60103168</t>
+          <t>81808123</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
+          <t>SHINA</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>CHUÑO</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>GILBERTO GABRIEL</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F496" t="n">
+        <v>8</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>28/03/2018</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>28/03/2023</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M496" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>80421441</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
           <t>SITICONANTSI</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>AVENCHARI</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>FRAY RIBALDO</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr">
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>AMPATI</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>LEONARDO</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
         <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F496" t="n">
-        <v>20</v>
-      </c>
-      <c r="G496" t="inlineStr">
-        <is>
-          <t>21/01/2006</t>
-        </is>
-      </c>
-      <c r="H496" t="inlineStr">
-        <is>
-          <t>3.JOVEN</t>
-        </is>
-      </c>
-      <c r="I496" t="inlineStr">
-        <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
-        </is>
-      </c>
-      <c r="J496" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K496" t="inlineStr">
+      <c r="F497" t="n">
+        <v>47</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>02/01/1979</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
         <is>
           <t>19/12/2012</t>
-        </is>
-      </c>
-      <c r="L496" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M496" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr"/>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>SITICONANTSI</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>ROSALES</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F497" t="n">
-        <v>1</v>
-      </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>15/03/2025</t>
-        </is>
-      </c>
-      <c r="H497" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I497" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
-      <c r="J497" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K497" t="inlineStr">
-        <is>
-          <t>15/03/2025</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -31634,22 +31626,22 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>20086239</t>
+          <t>60103167</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>SITICONATZI</t>
+          <t>SITICONANTSI</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>AMPATI</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>CHAPIAMA</t>
+          <t>YONER</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -31658,21 +31650,21 @@
         </is>
       </c>
       <c r="F498" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>01/01/1972</t>
+          <t>06/12/2000</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
@@ -31697,12 +31689,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>82369302</t>
+          <t>60103168</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>SITICONATZI</t>
+          <t>SITICONANTSI</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -31712,95 +31704,91 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>YUNET YULEISI</t>
+          <t>FRAY RIBALDO</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F499" t="n">
+        <v>20</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>21/01/2006</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>19/12/2012</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M499" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr"/>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>SITICONANTSI</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>ROSALES</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F499" t="n">
-        <v>3</v>
-      </c>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>13/09/2023</t>
-        </is>
-      </c>
-      <c r="H499" t="inlineStr">
+      <c r="F500" t="n">
+        <v>1</v>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>15/03/2025</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I499" t="inlineStr">
+      <c r="I500" t="inlineStr">
         <is>
           <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
-      <c r="J499" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K499" t="inlineStr">
-        <is>
-          <t>24/05/2024</t>
-        </is>
-      </c>
-      <c r="L499" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M499" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>48099744</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>SITICONATZI</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>CAMAITERI</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>YULI</t>
-        </is>
-      </c>
-      <c r="E500" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F500" t="n">
-        <v>33</v>
-      </c>
-      <c r="G500" t="inlineStr">
-        <is>
-          <t>12/07/1993</t>
-        </is>
-      </c>
-      <c r="H500" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I500" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
       <c r="J500" t="inlineStr">
         <is>
           <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
@@ -31808,7 +31796,7 @@
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>29/05/2020</t>
+          <t>15/03/2025</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -31823,7 +31811,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>60401472</t>
+          <t>20086239</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -31833,30 +31821,30 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>AMPATI</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>LIZBETH</t>
+          <t>CHAPIAMA</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>29/01/1998</t>
+          <t>01/01/1972</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31871,7 +31859,7 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -31886,7 +31874,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>74805383</t>
+          <t>82369302</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -31896,35 +31884,35 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>CLEVER</t>
+          <t>YUNET YULEISI</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>30/06/2003</t>
+          <t>13/09/2023</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
@@ -31934,7 +31922,7 @@
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>24/05/2024</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
@@ -31949,7 +31937,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>60401486</t>
+          <t>48099744</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -31964,7 +31952,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>MIRIAN GLADIS</t>
+          <t>YULI</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -31973,21 +31961,21 @@
         </is>
       </c>
       <c r="F503" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>09/08/2008</t>
+          <t>12/07/1993</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
@@ -31997,7 +31985,7 @@
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>29/05/2020</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
@@ -32012,7 +32000,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>60401485</t>
+          <t>60401472</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -32027,20 +32015,20 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>LLEISON CHAPIAMA</t>
+          <t>LIZBETH</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>09/08/2008</t>
+          <t>29/01/1998</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -32050,7 +32038,7 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
@@ -32075,45 +32063,45 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>20086262</t>
+          <t>74805383</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>SITIKONANTZI</t>
+          <t>SITICONATZI</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>TANIA</t>
+          <t>CLEVER</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>04/01/1962</t>
+          <t>30/06/2003</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
@@ -32123,7 +32111,7 @@
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>14/11/2011</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -32138,45 +32126,45 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>80085661</t>
+          <t>60401486</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>SITIKONANTZI</t>
+          <t>SITICONATZI</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>LUCIANO</t>
+          <t>MIRIAN GLADIS</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F506" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>21/07/1974</t>
+          <t>09/08/2008</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
@@ -32201,22 +32189,22 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>74773340</t>
+          <t>60401485</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>SITIKONANTZI</t>
+          <t>SITICONATZI</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>EULOGIO</t>
+          <t>LLEISON CHAPIAMA</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -32225,11 +32213,11 @@
         </is>
       </c>
       <c r="F507" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>04/09/1998</t>
+          <t>09/08/2008</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -32239,7 +32227,7 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
@@ -32264,7 +32252,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>74771581</t>
+          <t>20086262</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -32274,12 +32262,12 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>BERTI LUZ SENAIDA</t>
+          <t>TANIA</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -32288,21 +32276,21 @@
         </is>
       </c>
       <c r="F508" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>30/09/2000</t>
+          <t>04/01/1962</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
@@ -32312,7 +32300,7 @@
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>14/11/2011</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -32327,7 +32315,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>74773339</t>
+          <t>80085661</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -32337,12 +32325,12 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>LUIS JHANS</t>
+          <t>LUCIANO</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -32351,21 +32339,21 @@
         </is>
       </c>
       <c r="F509" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>22/06/2003</t>
+          <t>21/07/1974</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
@@ -32375,7 +32363,7 @@
       </c>
       <c r="K509" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
@@ -32390,7 +32378,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>63255882</t>
+          <t>74773340</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -32405,20 +32393,20 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>LIZ ANI</t>
+          <t>EULOGIO</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F510" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>13/12/2005</t>
+          <t>04/09/1998</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -32428,7 +32416,7 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
@@ -32453,7 +32441,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>63255883</t>
+          <t>74771581</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -32468,20 +32456,20 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>MARCOS ANTONIO</t>
+          <t>BERTI LUZ SENAIDA</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>28/01/2008</t>
+          <t>30/09/2000</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -32516,7 +32504,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>62690584</t>
+          <t>74773339</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -32531,7 +32519,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>ULIVER RAUL</t>
+          <t>LUIS JHANS</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -32540,21 +32528,21 @@
         </is>
       </c>
       <c r="F512" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>22/03/2012</t>
+          <t>22/06/2003</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
@@ -32564,7 +32552,7 @@
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>09/06/2015</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
@@ -32579,7 +32567,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>81183715</t>
+          <t>63255882</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -32594,30 +32582,30 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>JHAN JAIRO LUCIANO</t>
+          <t>LIZ ANI</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F513" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>25/02/2016</t>
+          <t>13/12/2005</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
@@ -32627,7 +32615,7 @@
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>18/05/2021</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -32642,22 +32630,22 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>47932472</t>
+          <t>63255883</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>SITIKONANTZI</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>JHONATAN</t>
+          <t>MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -32666,21 +32654,21 @@
         </is>
       </c>
       <c r="F514" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>20/09/1993</t>
+          <t>28/01/2008</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
@@ -32690,7 +32678,7 @@
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t>06/04/2015</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
@@ -32705,45 +32693,45 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>94321235</t>
+          <t>62690584</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>SITIKONANTZI</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>JAZMIN CATALEYA</t>
+          <t>ULIVER RAUL</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F515" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>20/07/2025</t>
+          <t>22/03/2012</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
@@ -32753,7 +32741,7 @@
       </c>
       <c r="K515" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>09/06/2015</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
@@ -32768,22 +32756,22 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>77246048</t>
+          <t>81183715</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>SITIKONANTZI</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>EDWIN</t>
+          <t>JHAN JAIRO LUCIANO</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -32792,21 +32780,21 @@
         </is>
       </c>
       <c r="F516" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>29/11/1996</t>
+          <t>25/02/2016</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
@@ -32816,7 +32804,7 @@
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>18/05/2021</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
@@ -32831,22 +32819,22 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>94193727</t>
+          <t>47932472</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>CARRION</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>HANIEL HEFER</t>
+          <t>JHONATAN</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -32855,82 +32843,86 @@
         </is>
       </c>
       <c r="F517" t="n">
+        <v>33</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>20/09/1993</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>06/04/2015</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M517" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>94321235</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>TAIPE</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>ROJAS</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>JAZMIN CATALEYA</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F518" t="n">
         <v>1</v>
       </c>
-      <c r="G517" t="inlineStr">
-        <is>
-          <t>23/03/2025</t>
-        </is>
-      </c>
-      <c r="H517" t="inlineStr">
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>20/07/2025</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I517" t="inlineStr">
+      <c r="I518" t="inlineStr">
         <is>
           <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
-      <c r="J517" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K517" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="L517" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M517" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr"/>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>TORRES</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>MASHICOLI</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F518" t="n">
-        <v>0</v>
-      </c>
-      <c r="G518" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="H518" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I518" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
       <c r="J518" t="inlineStr">
         <is>
           <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
@@ -32938,7 +32930,7 @@
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
@@ -32953,27 +32945,27 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>49091621</t>
+          <t>77246048</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>TORREZ</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>MAGDALENA</t>
+          <t>EDWIN</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F519" t="n">
@@ -32981,7 +32973,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>05/09/1996</t>
+          <t>29/11/1996</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -32991,7 +32983,7 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
@@ -33001,7 +32993,7 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -33016,22 +33008,22 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>63452821</t>
+          <t>94193727</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>TUANAMA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>CARRION</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>FHUSTO PASTOR</t>
+          <t>HANIEL HEFER</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -33040,11 +33032,11 @@
         </is>
       </c>
       <c r="F520" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>06/04/2016</t>
+          <t>23/03/2025</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -33054,7 +33046,7 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
@@ -33064,7 +33056,7 @@
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>18/05/2021</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -33077,37 +33069,33 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>82164071</t>
-        </is>
-      </c>
+      <c r="A521" t="inlineStr"/>
       <c r="B521" t="inlineStr">
         <is>
-          <t>UGARTE</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>MASHICOLI</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>NAYTI CLISMETH</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F521" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -33127,7 +33115,7 @@
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -33142,22 +33130,22 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>91007272</t>
+          <t>49091621</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>URQUIA</t>
+          <t>TORREZ</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>SITICONATZI</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>MIA BETSABE</t>
+          <t>MAGDALENA</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -33166,21 +33154,21 @@
         </is>
       </c>
       <c r="F522" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>14/10/2018</t>
+          <t>05/09/1996</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
@@ -33190,7 +33178,7 @@
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>14/10/2023</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -33205,22 +33193,22 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>94353375</t>
+          <t>63452821</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>URQUIA</t>
+          <t>TUANAMA</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>SITICONATZI</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>ANGEL GABRIEL</t>
+          <t>FHUSTO PASTOR</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -33229,82 +33217,86 @@
         </is>
       </c>
       <c r="F523" t="n">
+        <v>10</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>06/04/2016</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>18/05/2021</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M523" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>82164071</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>UGARTE</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>ARIAS</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>NAYTI CLISMETH</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F524" t="n">
         <v>1</v>
       </c>
-      <c r="G523" t="inlineStr">
-        <is>
-          <t>14/08/2025</t>
-        </is>
-      </c>
-      <c r="H523" t="inlineStr">
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I523" t="inlineStr">
+      <c r="I524" t="inlineStr">
         <is>
           <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
-      <c r="J523" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K523" t="inlineStr">
-        <is>
-          <t>05/12/2025</t>
-        </is>
-      </c>
-      <c r="L523" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M523" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr"/>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>VARGAS</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>MIERIANO</t>
-        </is>
-      </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="E524" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F524" t="n">
-        <v>2</v>
-      </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>22/05/2024</t>
-        </is>
-      </c>
-      <c r="H524" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I524" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
       <c r="J524" t="inlineStr">
         <is>
           <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
@@ -33312,7 +33304,7 @@
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>22/05/2024</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
@@ -33327,22 +33319,22 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>94428874</t>
+          <t>91007272</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>URQUIA</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>SAMUEL</t>
+          <t>SITICONATZI</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>LUZ NATALY MEYLI</t>
+          <t>MIA BETSABE</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -33351,11 +33343,11 @@
         </is>
       </c>
       <c r="F525" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>21/10/2025</t>
+          <t>14/10/2018</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -33365,7 +33357,7 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
@@ -33375,7 +33367,7 @@
       </c>
       <c r="K525" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>14/10/2023</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
@@ -33390,22 +33382,22 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>81992660</t>
+          <t>94353375</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>URQUIA</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>SITICONATZI</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>DEYSER ESNAYDER</t>
+          <t>ANGEL GABRIEL</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -33414,11 +33406,11 @@
         </is>
       </c>
       <c r="F526" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -33438,7 +33430,7 @@
       </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t>06/01/2023</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
@@ -33453,108 +33445,104 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>82000182</t>
+          <t>46282309</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>VALDERRAMA</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>GISANIA</t>
+          <t>GUILLERMO</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F527" t="n">
+        <v>37</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>26/12/1989</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M527" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr"/>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>VARGAS</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>MIERIANO</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="F527" t="n">
-        <v>8</v>
-      </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>11/12/2018</t>
-        </is>
-      </c>
-      <c r="H527" t="inlineStr">
+      <c r="F528" t="n">
+        <v>2</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>22/05/2024</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I527" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J527" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K527" t="inlineStr">
-        <is>
-          <t>20/07/2024</t>
-        </is>
-      </c>
-      <c r="L527" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M527" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>61604387</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>ZABALETA</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>FLORES</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>JHASMIN GUISELLA</t>
-        </is>
-      </c>
-      <c r="E528" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F528" t="n">
-        <v>23</v>
-      </c>
-      <c r="G528" t="inlineStr">
-        <is>
-          <t>10/06/2003</t>
-        </is>
-      </c>
-      <c r="H528" t="inlineStr">
-        <is>
-          <t>3.JOVEN</t>
-        </is>
-      </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
@@ -33564,7 +33552,7 @@
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>22/05/2024</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -33579,35 +33567,35 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>81899399</t>
+          <t>94428874</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>ZANDOVAL</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>CHUBIAVANTI</t>
+          <t>SAMUEL</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>ANDERSON</t>
+          <t>LUZ NATALY MEYLI</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F529" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>17/06/2021</t>
+          <t>21/10/2025</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -33617,7 +33605,7 @@
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
@@ -33627,7 +33615,7 @@
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
@@ -33642,35 +33630,35 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>94018964</t>
+          <t>81992660</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>ZANDOVAL</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>CHUBIAVANTI</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>ELIZABET</t>
+          <t>DEYSER ESNAYDER</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F530" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>17/10/2024</t>
+          <t>15/10/2021</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -33690,7 +33678,7 @@
       </c>
       <c r="K530" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>06/01/2023</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
@@ -33705,22 +33693,22 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>82206035</t>
+          <t>82000182</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>ZEBASTIAN</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>MILAGROS</t>
+          <t>GISANIA</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -33729,11 +33717,11 @@
         </is>
       </c>
       <c r="F531" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>25/12/2025</t>
+          <t>11/12/2018</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -33743,7 +33731,7 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
@@ -33753,7 +33741,7 @@
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
@@ -33768,45 +33756,45 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>93047747</t>
+          <t>61604387</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>ZUCA</t>
+          <t>ZABALETA</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>ANTHONY</t>
+          <t>JHASMIN GUISELLA</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F532" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>05/09/2022</t>
+          <t>10/06/2003</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
@@ -33816,7 +33804,7 @@
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>19/03/2024</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -33831,45 +33819,45 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>62000445</t>
+          <t>81899399</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>ÑACO</t>
+          <t>ZANDOVAL</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>SEBERIANO</t>
+          <t>CHUBIAVANTI</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>SUSANA</t>
+          <t>ANDERSON</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F533" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>14/10/2000</t>
+          <t>17/06/2021</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
@@ -33879,7 +33867,7 @@
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>05/02/2015</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -33894,63 +33882,315 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
+          <t>94018964</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>ZANDOVAL</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>CHUBIAVANTI</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>ELIZABET</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F534" t="n">
+        <v>2</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>17/10/2024</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M534" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>82206035</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>ZEBASTIAN</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>MILAGROS</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F535" t="n">
+        <v>1</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>25/12/2025</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M535" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>93047747</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>ZUCA</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>NAVARRO</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>ANTHONY</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F536" t="n">
+        <v>4</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>05/09/2022</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>19/03/2024</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M536" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>62000445</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>ÑACO</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>SEBERIANO</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>SUSANA</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F537" t="n">
+        <v>26</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>14/10/2000</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>05/02/2015</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M537" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
           <t>62000432</t>
         </is>
       </c>
-      <c r="B534" t="inlineStr">
+      <c r="B538" t="inlineStr">
         <is>
           <t>ÑACO</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr">
+      <c r="C538" t="inlineStr">
         <is>
           <t>SEBERIANO</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr">
+      <c r="D538" t="inlineStr">
         <is>
           <t>EMANUEL DANIEL</t>
         </is>
       </c>
-      <c r="E534" t="inlineStr">
+      <c r="E538" t="inlineStr">
         <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F534" t="n">
+      <c r="F538" t="n">
         <v>16</v>
       </c>
-      <c r="G534" t="inlineStr">
+      <c r="G538" t="inlineStr">
         <is>
           <t>24/12/2010</t>
         </is>
       </c>
-      <c r="H534" t="inlineStr">
+      <c r="H538" t="inlineStr">
         <is>
           <t>2.ADOLESCENTE</t>
         </is>
       </c>
-      <c r="I534" t="inlineStr">
+      <c r="I538" t="inlineStr">
         <is>
           <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
-      <c r="J534" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K534" t="inlineStr">
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
         <is>
           <t>05/02/2015</t>
         </is>
       </c>
-      <c r="L534" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M534" t="n">
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M538" t="n">
         <v>120608</v>
       </c>
     </row>

--- a/exports/466_santa-rosita-de-shirintiari.xlsx
+++ b/exports/466_santa-rosita-de-shirintiari.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M538"/>
+  <dimension ref="A1:M534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24280,12 +24280,12 @@
       <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
-          <t>MOCHI</t>
+          <t>MORI</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>MISHICOLI</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -24299,11 +24299,11 @@
         </is>
       </c>
       <c r="F381" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>20/01/2022</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -24323,7 +24323,7 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>20/01/2023</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -24336,7 +24336,11 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr"/>
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>62000399</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>MORI</t>
@@ -24344,12 +24348,12 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>CAMAYTERI</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>TIMOTEO RIVER</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -24358,21 +24362,21 @@
         </is>
       </c>
       <c r="F382" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>20/01/2022</t>
+          <t>24/04/2005</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
@@ -24382,7 +24386,7 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>20/01/2023</t>
+          <t>21/12/2012</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -24397,7 +24401,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>62000399</t>
+          <t>61604380</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -24412,7 +24416,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>TIMOTEO RIVER</t>
+          <t>RUMI</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -24421,11 +24425,11 @@
         </is>
       </c>
       <c r="F383" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>24/04/2005</t>
+          <t>20/12/2007</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -24460,7 +24464,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>61604380</t>
+          <t>62273984</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -24475,25 +24479,25 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>RUMI</t>
+          <t>CECILIA</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F384" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>20/12/2007</t>
+          <t>09/06/2010</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -24523,7 +24527,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>62273984</t>
+          <t>63452734</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -24538,20 +24542,20 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>CECILIA</t>
+          <t>MISAEL</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F385" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>09/06/2010</t>
+          <t>10/02/2013</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -24571,7 +24575,7 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>21/12/2012</t>
+          <t>06/08/2014</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -24586,7 +24590,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>63452734</t>
+          <t>80084338</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -24596,35 +24600,35 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>CAMAYTERI</t>
+          <t>VELA</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>MISAEL</t>
+          <t>JUANA</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F386" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>10/02/2013</t>
+          <t>15/01/1976</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
@@ -24634,7 +24638,7 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>06/08/2014</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -24649,7 +24653,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>80084338</t>
+          <t>80085675</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24664,7 +24668,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>JUANA</t>
+          <t>IRMA</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -24673,11 +24677,11 @@
         </is>
       </c>
       <c r="F387" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>15/01/1976</t>
+          <t>05/04/1978</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24712,7 +24716,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>80085675</t>
+          <t>44708509</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -24727,20 +24731,20 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>IRMA</t>
+          <t>ARMANDO</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F388" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>05/04/1978</t>
+          <t>09/09/1984</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -24760,7 +24764,7 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>21/12/2012</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -24775,7 +24779,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>44708509</t>
+          <t>45183606</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -24790,7 +24794,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>ARMANDO</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -24799,11 +24803,11 @@
         </is>
       </c>
       <c r="F389" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>09/09/1984</t>
+          <t>03/04/1985</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -24823,7 +24827,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>21/12/2012</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -24838,35 +24842,35 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>45183606</t>
+          <t>61737452</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>MORI</t>
+          <t>NAPO</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>NATALIA</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F390" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>03/04/1985</t>
+          <t>08/08/1996</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24886,7 +24890,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>01/06/2015</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -24901,22 +24905,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>61737452</t>
+          <t>94076107</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>NAPO</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>ASHISHO</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>NATALIA</t>
+          <t>KEYSSI AYTANA</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -24925,21 +24929,21 @@
         </is>
       </c>
       <c r="F391" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>08/08/1996</t>
+          <t>10/12/2024</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
@@ -24949,7 +24953,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>01/06/2015</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -24964,7 +24968,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>94076107</t>
+          <t>82164062</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -24974,12 +24978,12 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>ASHISHO</t>
+          <t>CRISTOBAL</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>KEYSSI AYTANA</t>
+          <t>THASHA ARIANA</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -24988,11 +24992,11 @@
         </is>
       </c>
       <c r="F392" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>10/12/2024</t>
+          <t>25/11/2023</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25012,7 +25016,7 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -25027,7 +25031,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>82164062</t>
+          <t>72611782</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25037,12 +25041,12 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>CRISTOBAL</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>THASHA ARIANA</t>
+          <t>LUCY IVETT</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -25051,21 +25055,21 @@
         </is>
       </c>
       <c r="F393" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>25/11/2023</t>
+          <t>09/12/1994</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -25075,7 +25079,7 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>10/11/2011</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -25090,7 +25094,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>72611782</t>
+          <t>93754592</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25100,12 +25104,12 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>LUCY IVETT</t>
+          <t>SUNI ARELY</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -25114,21 +25118,21 @@
         </is>
       </c>
       <c r="F394" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>09/12/1994</t>
+          <t>25/02/2024</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
@@ -25138,7 +25142,7 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>10/11/2011</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -25153,22 +25157,22 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>72611784</t>
+          <t>72291251</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>OMPIQUIRI</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>ADARMES</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>BERLY</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -25177,16 +25181,16 @@
         </is>
       </c>
       <c r="F395" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>11/09/1997</t>
+          <t>07/04/1991</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -25201,7 +25205,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -25216,22 +25220,22 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>93754592</t>
+          <t>20980081</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>OMPIQUIRI</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>CASHANTIOTE</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>SUNI ARELY</t>
+          <t>CESARINA</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -25240,21 +25244,21 @@
         </is>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>25/02/2024</t>
+          <t>07/10/1938</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
@@ -25264,7 +25268,7 @@
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>06/04/2015</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -25279,22 +25283,22 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>72291251</t>
+          <t>20086251</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>OMPIQUIRI</t>
+          <t>ONICA</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>ADARMES</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>ROGELIO</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -25303,11 +25307,11 @@
         </is>
       </c>
       <c r="F397" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>07/04/1991</t>
+          <t>01/03/1974</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -25317,7 +25321,7 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -25327,7 +25331,7 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -25342,45 +25346,45 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>20980081</t>
+          <t>76989075</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>OMPIQUIRI</t>
+          <t>ONICA</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>CASHANTIOTE</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CESARINA</t>
+          <t>ALEXANDER</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>07/10/1938</t>
+          <t>09/12/1997</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
@@ -25390,7 +25394,7 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>06/04/2015</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -25405,7 +25409,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>20086251</t>
+          <t>61551258</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -25415,35 +25419,35 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>ROGELIO</t>
+          <t>MARI CARMEN</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>01/03/1974</t>
+          <t>02/12/2000</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -25468,7 +25472,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>76989075</t>
+          <t>61551259</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -25483,7 +25487,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>ALEXANDER</t>
+          <t>ELMER ROGELIO</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -25492,11 +25496,11 @@
         </is>
       </c>
       <c r="F400" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>09/12/1997</t>
+          <t>05/04/2004</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -25506,7 +25510,7 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
@@ -25531,7 +25535,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>61551258</t>
+          <t>60401496</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -25546,7 +25550,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>MARI CARMEN</t>
+          <t>LIUZ DELIA</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -25555,11 +25559,11 @@
         </is>
       </c>
       <c r="F401" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>02/12/2000</t>
+          <t>25/11/2008</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -25594,7 +25598,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>61551259</t>
+          <t>81183663</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -25604,35 +25608,35 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>KAMAITERI</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>ELMER ROGELIO</t>
+          <t>EVELYN SANYURI</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F402" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>05/04/2004</t>
+          <t>07/10/2014</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -25642,7 +25646,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>09/06/2015</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -25657,7 +25661,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>60401496</t>
+          <t>81808338</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -25667,35 +25671,35 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>LIUZ DELIA</t>
+          <t>WILIAM ALFREDO</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F403" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>25/11/2008</t>
+          <t>13/09/2018</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -25705,7 +25709,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>13/09/2023</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -25720,7 +25724,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>81183663</t>
+          <t>82003245</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -25730,12 +25734,12 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>KAMAITERI</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>EVELYN SANYURI</t>
+          <t>JHUMI SAHIRED</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -25744,21 +25748,21 @@
         </is>
       </c>
       <c r="F404" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>07/10/2014</t>
+          <t>04/05/2023</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -25768,7 +25772,7 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>09/06/2015</t>
+          <t>01/09/2023</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -25783,22 +25787,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>81808338</t>
+          <t>94212779</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>ONICA</t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>WILIAM ALFREDO</t>
+          <t>YOSHIRO BONIFACIO</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -25807,11 +25811,11 @@
         </is>
       </c>
       <c r="F405" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>13/09/2018</t>
+          <t>08/04/2025</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -25821,7 +25825,7 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -25831,7 +25835,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>13/09/2023</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -25846,22 +25850,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>82003245</t>
+          <t>44708511</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>ONICA</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>JHUMI SAHIRED</t>
+          <t>ALEJANDRINA</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -25870,21 +25874,21 @@
         </is>
       </c>
       <c r="F406" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>04/05/2023</t>
+          <t>24/06/1981</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
@@ -25894,7 +25898,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>01/09/2023</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -25909,45 +25913,45 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>94212779</t>
+          <t>46442728</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>YOSHIRO BONIFACIO</t>
+          <t>MARCELINA</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F407" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>08/04/2025</t>
+          <t>21/01/1984</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
@@ -25957,7 +25961,7 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -25972,7 +25976,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>44708511</t>
+          <t>74422358</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -25987,7 +25991,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>ALEJANDRINA</t>
+          <t>LUCILA</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -25996,16 +26000,16 @@
         </is>
       </c>
       <c r="F408" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>24/06/1981</t>
+          <t>17/12/1998</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -26020,7 +26024,7 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
@@ -26035,7 +26039,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>46442728</t>
+          <t>21009888</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26045,30 +26049,30 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>MARCELINA</t>
+          <t>ABRAN</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>21/01/1984</t>
+          <t>15/08/1964</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -26098,35 +26102,35 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>74422358</t>
+          <t>60300885</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>PEGO</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>LUCILA</t>
+          <t>JENNER LUIS</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>17/12/1998</t>
+          <t>28/12/2006</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26136,7 +26140,7 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -26146,7 +26150,7 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -26161,40 +26165,40 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>21009888</t>
+          <t>62690625</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>PEGO</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>ABRAN</t>
+          <t>LLEYSIN MARICTZA</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>15/08/1964</t>
+          <t>26/05/2013</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -26209,7 +26213,7 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>09/06/2015</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -26224,7 +26228,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>60300885</t>
+          <t>80421430</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -26234,12 +26238,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>JENNER LUIS</t>
+          <t>CESAR</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -26248,21 +26252,21 @@
         </is>
       </c>
       <c r="F412" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>28/12/2006</t>
+          <t>09/11/1979</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
@@ -26287,22 +26291,22 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>62690625</t>
+          <t>81872647</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>PEGO</t>
+          <t>PERALTA</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>BLANCO</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>LLEYSIN MARICTZA</t>
+          <t>FELICIA LINDA</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -26311,21 +26315,21 @@
         </is>
       </c>
       <c r="F413" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>26/05/2013</t>
+          <t>15/02/2021</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -26335,7 +26339,7 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>09/06/2015</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
@@ -26350,40 +26354,40 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>80421430</t>
+          <t>62809060</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>PEGO</t>
+          <t>PEZO</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>CAMINTI</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>CESAR</t>
+          <t>ELITA</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>09/11/1979</t>
+          <t>12/09/2001</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -26398,7 +26402,7 @@
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>08/05/2012</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
@@ -26413,22 +26417,22 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>81872647</t>
+          <t>48562212</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>PERALTA</t>
+          <t>PINHO</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>BLANCO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>FELICIA LINDA</t>
+          <t>VERONICA ANGELICA</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -26437,21 +26441,21 @@
         </is>
       </c>
       <c r="F415" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>15/02/2021</t>
+          <t>25/05/1988</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -26461,7 +26465,7 @@
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>17/11/2012</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
@@ -26476,45 +26480,45 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>62809060</t>
+          <t>82003212</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>PEZO</t>
+          <t>PIROCO</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>CAMINTI</t>
+          <t>KAMAITERI</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>ELITA</t>
+          <t>PABLO</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>12/09/2001</t>
+          <t>30/05/2022</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -26524,7 +26528,7 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>08/05/2012</t>
+          <t>07/01/2023</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
@@ -26539,22 +26543,22 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>48562212</t>
+          <t>82369305</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>PINHO</t>
+          <t>PLASHICO</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MISHICOLI</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>VERONICA ANGELICA</t>
+          <t>ARLETH ANALI BETH</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -26563,21 +26567,21 @@
         </is>
       </c>
       <c r="F417" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>25/05/1988</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
@@ -26587,7 +26591,7 @@
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>17/11/2012</t>
+          <t>27/05/2024</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -26602,45 +26606,45 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>82003212</t>
+          <t>62274147</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>PIROCO</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>KAMAITERI</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>PABLO</t>
+          <t>ROSSY BELL</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>30/05/2022</t>
+          <t>14/08/2012</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -26650,7 +26654,7 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>07/01/2023</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -26665,22 +26669,22 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>82369305</t>
+          <t>93857741</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>PLASHICO</t>
+          <t>PRADO</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>MISHICOLI</t>
+          <t>LUCRECIA</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>ARLETH ANALI BETH</t>
+          <t>KEYMI SHIOMY</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -26689,11 +26693,11 @@
         </is>
       </c>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>02/06/2024</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -26713,7 +26717,7 @@
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>27/05/2024</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
@@ -26728,22 +26732,22 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>62274147</t>
+          <t>80085596</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>QUENTIMARI</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MARIANO</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>ROSSY BELL</t>
+          <t>GLORIA</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -26752,21 +26756,21 @@
         </is>
       </c>
       <c r="F420" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>14/08/2012</t>
+          <t>13/04/1979</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
@@ -26776,7 +26780,7 @@
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
@@ -26791,35 +26795,35 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>93857741</t>
+          <t>81971708</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>PRADO</t>
+          <t>QUENTISHA</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>LUCRECIA</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>KEYMI SHIOMY</t>
+          <t>LANFAN TABALU</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F421" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>02/06/2024</t>
+          <t>02/11/2023</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -26839,7 +26843,7 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>22/07/2024</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -26854,35 +26858,35 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>80085596</t>
+          <t>60401473</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>QUENTIMARI</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>MARIANO</t>
+          <t>AMPATI</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>GLORIA</t>
+          <t>CRISTIAN</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>13/04/1979</t>
+          <t>03/05/1995</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -26917,22 +26921,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>81971708</t>
+          <t>60300853</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>QUENTISHA</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>AMPATI</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>LANFAN TABALU</t>
+          <t>EFRAIN</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -26941,21 +26945,21 @@
         </is>
       </c>
       <c r="F423" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>02/11/2023</t>
+          <t>14/04/2007</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -26965,7 +26969,7 @@
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>22/07/2024</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
@@ -26980,7 +26984,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>60401473</t>
+          <t>21009964</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -26990,12 +26994,12 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>AMPATI</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>CRISTIAN</t>
+          <t>TEOFILO</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -27004,11 +27008,11 @@
         </is>
       </c>
       <c r="F424" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>03/05/1995</t>
+          <t>05/01/1969</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -27043,7 +27047,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>60300853</t>
+          <t>21009957</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -27053,35 +27057,35 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>AMPATI</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>EFRAIN</t>
+          <t>IRENE</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F425" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>14/04/2007</t>
+          <t>08/08/1972</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -27091,7 +27095,7 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>30/10/2012</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
@@ -27106,7 +27110,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>21009964</t>
+          <t>81808325</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -27116,12 +27120,12 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>DIQUES</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>TEOFILO</t>
+          <t>YELSIN GABRIEL</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -27130,16 +27134,16 @@
         </is>
       </c>
       <c r="F426" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>05/01/1969</t>
+          <t>16/02/2018</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -27154,7 +27158,7 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>16/02/2023</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -27169,7 +27173,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>21009957</t>
+          <t>82369324</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -27179,12 +27183,12 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>SHINA</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>IRENE</t>
+          <t>KEYLI JULIET</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -27193,21 +27197,21 @@
         </is>
       </c>
       <c r="F427" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>08/08/1972</t>
+          <t>13/02/2024</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -27217,7 +27221,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>30/10/2012</t>
+          <t>27/05/2024</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -27232,35 +27236,35 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>81808325</t>
+          <t>81808102</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>DIQUES</t>
+          <t>VALDERRAMA</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>YELSIN GABRIEL</t>
+          <t>LYA MERCEDEZ</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>16/02/2018</t>
+          <t>22/07/2015</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -27270,7 +27274,7 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -27280,7 +27284,7 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>16/02/2023</t>
+          <t>12/09/2020</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -27295,45 +27299,45 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>82369324</t>
+          <t>80717362</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>RATTERI</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>SHINA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>KEYLI JULIET</t>
+          <t>JUAN PABLO</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>13/02/2024</t>
+          <t>04/03/2005</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
@@ -27343,7 +27347,7 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>27/05/2024</t>
+          <t>21/02/2022</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -27358,45 +27362,45 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>81808102</t>
+          <t>77698244</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>RATTERI</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>VALDERRAMA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>LYA MERCEDEZ</t>
+          <t>PIERO LUIGI</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>22/07/2015</t>
+          <t>18/08/2005</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
@@ -27406,7 +27410,7 @@
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>12/09/2020</t>
+          <t>29/10/2012</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
@@ -27421,7 +27425,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>80717362</t>
+          <t>00150663</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -27431,12 +27435,12 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>JUAN PABLO</t>
+          <t>LUIS ANGEL</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -27445,16 +27449,16 @@
         </is>
       </c>
       <c r="F431" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>04/03/2005</t>
+          <t>06/02/1955</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -27469,7 +27473,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>21/02/2022</t>
+          <t>29/10/2012</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -27484,45 +27488,45 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>77698244</t>
+          <t>81183723</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>RATTERI</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>PIERO LUIGI</t>
+          <t>KATTERINE MIRIELA</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>18/08/2005</t>
+          <t>13/06/2015</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
@@ -27532,7 +27536,7 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>29/10/2012</t>
+          <t>12/09/2020</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -27547,35 +27551,35 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>00150663</t>
+          <t>20086279</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>RATTERI</t>
+          <t>REATEGUI</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>LUIS ANGEL</t>
+          <t>MARLENI</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>06/02/1955</t>
+          <t>05/07/1965</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -27595,7 +27599,7 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>29/10/2012</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
@@ -27610,45 +27614,45 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>81183723</t>
+          <t>44712764</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>REATEGUI</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>SAMANCHAQUI</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>KATTERINE MIRIELA</t>
+          <t>FAUSTO</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>13/06/2015</t>
+          <t>22/06/1959</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -27658,7 +27662,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>12/09/2020</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
@@ -27673,22 +27677,22 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>20086279</t>
+          <t>63191364</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>REATEGUI</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>MARLENI</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -27697,16 +27701,16 @@
         </is>
       </c>
       <c r="F435" t="n">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>05/07/1965</t>
+          <t>13/02/2003</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27721,7 +27725,7 @@
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>02/03/2015</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
@@ -27736,22 +27740,22 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>44712764</t>
+          <t>93747405</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>REATEGUI</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>SAMANCHAQUI</t>
+          <t>MELCHOR</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>FAUSTO</t>
+          <t>DYLAN JHARED EDUARDO</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -27760,21 +27764,21 @@
         </is>
       </c>
       <c r="F436" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>22/06/1959</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -27784,7 +27788,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
@@ -27799,22 +27803,22 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>63191364</t>
+          <t>73979687</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>HERMILA</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -27823,21 +27827,21 @@
         </is>
       </c>
       <c r="F437" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>13/02/2003</t>
+          <t>16/05/1995</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -27847,7 +27851,7 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>02/03/2015</t>
+          <t>17/04/2024</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
@@ -27860,25 +27864,29 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="inlineStr"/>
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>94620099</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>REVILLA</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>KAEL LEIN FRAIN</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F438" t="n">
@@ -27886,7 +27894,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27906,7 +27914,7 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
@@ -27919,33 +27927,37 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr"/>
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>92093102</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>AZENETH</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F439" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>03/11/2020</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27955,7 +27967,7 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -27965,7 +27977,7 @@
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -27980,22 +27992,22 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>93747405</t>
+          <t>23693751</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>MELCHOR</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>DYLAN JHARED EDUARDO</t>
+          <t>TEODORO</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -28004,21 +28016,21 @@
         </is>
       </c>
       <c r="F440" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>19/09/1974</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -28028,7 +28040,7 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -28043,22 +28055,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>73979687</t>
+          <t>93334714</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RUFINO</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>HERMILA</t>
+          <t>ASENETH SHANIN</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -28067,21 +28079,21 @@
         </is>
       </c>
       <c r="F441" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>16/05/1995</t>
+          <t>06/04/2023</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -28091,7 +28103,7 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -28106,45 +28118,45 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>94620099</t>
+          <t>62000412</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>REVILLA</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>KAEL LEIN FRAIN</t>
+          <t>BETMA</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F442" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2004</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -28154,7 +28166,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/10/2011</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -28169,22 +28181,22 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>92093102</t>
+          <t>21009889</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>AZENETH</t>
+          <t>TEREZA</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -28193,21 +28205,21 @@
         </is>
       </c>
       <c r="F443" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>03/11/2020</t>
+          <t>18/05/1958</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
@@ -28217,7 +28229,7 @@
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>18/10/2011</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
@@ -28232,35 +28244,35 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>23693751</t>
+          <t>71088552</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>TEODORO</t>
+          <t>CLISENCIA</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F444" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>19/09/1974</t>
+          <t>29/07/1995</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -28270,7 +28282,7 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
@@ -28280,7 +28292,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
@@ -28295,110 +28307,106 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>93334714</t>
+          <t>80084333</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>RUFINO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>ASENETH SHANIN</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F445" t="n">
+        <v>55</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>25/06/1971</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>20/12/2012</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M445" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr"/>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>CHUÑO</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F446" t="n">
         <v>3</v>
       </c>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>06/04/2023</t>
-        </is>
-      </c>
-      <c r="H445" t="inlineStr">
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>13/09/2023</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I445" t="inlineStr">
+      <c r="I446" t="inlineStr">
         <is>
           <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
-      <c r="J445" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K445" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="L445" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M445" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>62000412</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>RUIZ</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>AVENCHARI</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>BETMA</t>
-        </is>
-      </c>
-      <c r="E446" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F446" t="n">
-        <v>22</v>
-      </c>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>21/04/2004</t>
-        </is>
-      </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>3.JOVEN</t>
-        </is>
-      </c>
-      <c r="I446" t="inlineStr">
-        <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
-        </is>
-      </c>
       <c r="J446" t="inlineStr">
         <is>
           <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
@@ -28406,7 +28414,7 @@
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>18/10/2011</t>
+          <t>13/09/2023</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -28421,45 +28429,45 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>21009889</t>
+          <t>62273993</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>TEREZA</t>
+          <t>OSWALDO</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>18/05/1958</t>
+          <t>07/10/1996</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -28469,7 +28477,7 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>18/10/2011</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
@@ -28484,22 +28492,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>71088552</t>
+          <t>77802065</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>FIGUEROA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>CLISENCIA</t>
+          <t>VALERIA DEYSI</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -28508,16 +28516,16 @@
         </is>
       </c>
       <c r="F448" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>29/07/1995</t>
+          <t>21/06/2001</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -28532,7 +28540,7 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
@@ -28547,7 +28555,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>80084333</t>
+          <t>77802064</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -28557,104 +28565,108 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>VILCIA</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F449" t="n">
+        <v>24</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>14/09/2002</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>20/12/2012</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M449" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>61604357</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>JHONI CLEVER</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F449" t="n">
-        <v>55</v>
-      </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>25/06/1971</t>
-        </is>
-      </c>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I449" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J449" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K449" t="inlineStr">
+      <c r="F450" t="n">
+        <v>20</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>19/12/2006</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
         <is>
           <t>20/12/2012</t>
-        </is>
-      </c>
-      <c r="L449" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M449" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr"/>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>SANCHEZ</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>CHUÑO</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="E450" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F450" t="n">
-        <v>3</v>
-      </c>
-      <c r="G450" t="inlineStr">
-        <is>
-          <t>13/09/2023</t>
-        </is>
-      </c>
-      <c r="H450" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
-      <c r="J450" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K450" t="inlineStr">
-        <is>
-          <t>13/09/2023</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
@@ -28669,7 +28681,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>62273993</t>
+          <t>61604358</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -28684,7 +28696,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>OSWALDO</t>
+          <t>CLIVER</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -28693,16 +28705,16 @@
         </is>
       </c>
       <c r="F451" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>07/10/1996</t>
+          <t>14/12/2008</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28732,7 +28744,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>77802065</t>
+          <t>63452742</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -28742,35 +28754,35 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GARLIA</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>VALERIA DEYSI</t>
+          <t>MAYNER</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>21/06/2001</t>
+          <t>21/11/2012</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -28780,7 +28792,7 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>06/08/2014</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -28795,7 +28807,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>77802064</t>
+          <t>63452761</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -28805,12 +28817,12 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GARLIA</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>VILCIA</t>
+          <t>ELIANA</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -28819,21 +28831,21 @@
         </is>
       </c>
       <c r="F453" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>14/09/2002</t>
+          <t>28/01/2014</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -28843,7 +28855,7 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>20/10/2014</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -28858,7 +28870,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>61604357</t>
+          <t>80839080</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -28868,35 +28880,35 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>JHONI CLEVER</t>
+          <t>KEYSI CELINA</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>19/12/2006</t>
+          <t>17/01/2014</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -28906,7 +28918,7 @@
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>30/03/2016</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
@@ -28921,7 +28933,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>61604358</t>
+          <t>81367664</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -28931,12 +28943,12 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>CLIVER</t>
+          <t>RALY</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -28945,21 +28957,21 @@
         </is>
       </c>
       <c r="F455" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>14/12/2008</t>
+          <t>25/12/2015</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -28969,7 +28981,7 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>30/12/2020</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
@@ -28984,7 +28996,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>63452742</t>
+          <t>81808133</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -28994,12 +29006,12 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>GARLIA</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>MAYNER</t>
+          <t>YAYR</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -29008,21 +29020,21 @@
         </is>
       </c>
       <c r="F456" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>21/11/2012</t>
+          <t>21/01/2019</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -29032,7 +29044,7 @@
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>06/08/2014</t>
+          <t>21/01/2024</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -29047,7 +29059,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>63452761</t>
+          <t>82003232</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -29057,12 +29069,12 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>GARLIA</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>ELIANA</t>
+          <t>KATIA NICOL</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -29071,21 +29083,21 @@
         </is>
       </c>
       <c r="F457" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>28/01/2014</t>
+          <t>31/01/2023</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -29095,7 +29107,7 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>20/10/2014</t>
+          <t>05/06/2023</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -29110,7 +29122,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>80839080</t>
+          <t>63452862</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -29120,30 +29132,30 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>PANDURO</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>KEYSI CELINA</t>
+          <t>PAUL ALY</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F458" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>17/01/2014</t>
+          <t>25/09/2017</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -29158,7 +29170,7 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>30/03/2016</t>
+          <t>25/09/2022</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -29173,7 +29185,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>81367664</t>
+          <t>72575052</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -29183,12 +29195,12 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>RALY</t>
+          <t>IDELSON</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -29197,84 +29209,80 @@
         </is>
       </c>
       <c r="F459" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>25/12/2015</t>
+          <t>21/04/1994</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>19/12/2012</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M459" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr"/>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>VARGAS</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F460" t="n">
+        <v>2</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>19/05/2024</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I459" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J459" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K459" t="inlineStr">
-        <is>
-          <t>30/12/2020</t>
-        </is>
-      </c>
-      <c r="L459" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M459" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>81808133</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>SANCHEZ</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>KENTIMARI</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>YAYR</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F460" t="n">
-        <v>7</v>
-      </c>
-      <c r="G460" t="inlineStr">
-        <is>
-          <t>21/01/2019</t>
-        </is>
-      </c>
-      <c r="H460" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -29284,7 +29292,7 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>21/01/2024</t>
+          <t>19/05/2024</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -29299,27 +29307,27 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>82003232</t>
+          <t>82202905</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SANCHO</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>KATIA NICOL</t>
+          <t>CRISTIAN</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F461" t="n">
@@ -29327,7 +29335,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>31/01/2023</t>
+          <t>12/02/2023</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -29347,7 +29355,7 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>05/06/2023</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
@@ -29362,22 +29370,22 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>63452862</t>
+          <t>20086242</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>PANDURO</t>
+          <t>MISCAY</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>PAUL ALY</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -29386,16 +29394,16 @@
         </is>
       </c>
       <c r="F462" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>25/09/2017</t>
+          <t>05/04/1971</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -29410,7 +29418,7 @@
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>25/09/2022</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -29425,114 +29433,118 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>72575052</t>
+          <t>47477397</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>MISHICOLI</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>IDELSON</t>
+          <t>MELITA</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F463" t="n">
+        <v>35</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>25/10/1991</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>19/12/2012</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M463" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>62273934</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>MISHICOLI</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>PERCY</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F463" t="n">
-        <v>32</v>
-      </c>
-      <c r="G463" t="inlineStr">
-        <is>
-          <t>21/04/1994</t>
-        </is>
-      </c>
-      <c r="H463" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I463" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J463" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K463" t="inlineStr">
+      <c r="F464" t="n">
+        <v>20</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>22/07/2006</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
         <is>
           <t>19/12/2012</t>
-        </is>
-      </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M463" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr"/>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>SANCHEZ</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>VARGAS</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F464" t="n">
-        <v>2</v>
-      </c>
-      <c r="G464" t="inlineStr">
-        <is>
-          <t>19/05/2024</t>
-        </is>
-      </c>
-      <c r="H464" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I464" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
-      <c r="J464" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K464" t="inlineStr">
-        <is>
-          <t>19/05/2024</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
@@ -29547,45 +29559,45 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>82202905</t>
+          <t>63346015</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>SANCHO</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>MISHICOLI</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>CRISTIAN</t>
+          <t>LUZ MARIA</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F465" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>12/02/2023</t>
+          <t>22/09/2006</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
@@ -29595,7 +29607,7 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -29610,22 +29622,22 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>20086242</t>
+          <t>81932630</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>MISCAY</t>
+          <t>SHEVANCORI</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>RIMI</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -29634,21 +29646,21 @@
         </is>
       </c>
       <c r="F466" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>05/04/1971</t>
+          <t>02/05/2021</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
@@ -29658,7 +29670,7 @@
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
@@ -29673,45 +29685,45 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>47477397</t>
+          <t>72603687</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>SEBERIANO</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>MISHICOLI</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>MELITA</t>
+          <t>ELIO</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F467" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>25/10/1991</t>
+          <t>12/07/1998</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -29721,7 +29733,7 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -29736,22 +29748,22 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>62273934</t>
+          <t>80084344</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>SEBERIANO</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>MISHICOLI</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>PERCY</t>
+          <t>BENANCIO</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -29760,21 +29772,21 @@
         </is>
       </c>
       <c r="F468" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>22/07/2006</t>
+          <t>06/06/1976</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -29784,7 +29796,7 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
@@ -29799,22 +29811,22 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>63346015</t>
+          <t>48847636</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>SEBERIANO</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>MISHICOLI</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>LUZ MARIA</t>
+          <t>MERLY</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -29823,21 +29835,21 @@
         </is>
       </c>
       <c r="F469" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>22/09/2006</t>
+          <t>30/04/1985</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -29847,7 +29859,7 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>05/02/2015</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
@@ -29862,45 +29874,45 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>81932630</t>
+          <t>20086273</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SEMERI</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>SHEVANCORI</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>RIMI</t>
+          <t>DORITA</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F470" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>02/05/2021</t>
+          <t>26/01/1956</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -29910,7 +29922,7 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -29925,45 +29937,45 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>72603687</t>
+          <t>20086276</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>SEBERIANO</t>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>CHOMPATI</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>ELIO</t>
+          <t>CAROLA</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F471" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>12/07/1998</t>
+          <t>09/02/1968</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
@@ -29973,7 +29985,7 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>06/02/2015</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
@@ -29988,22 +30000,22 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>80084344</t>
+          <t>80430197</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>SEBERIANO</t>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>BENANCIO</t>
+          <t>USIAS</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -30012,11 +30024,11 @@
         </is>
       </c>
       <c r="F472" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>06/06/1976</t>
+          <t>09/01/1977</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -30026,7 +30038,7 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
@@ -30036,7 +30048,7 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>03/05/2024</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
@@ -30051,22 +30063,22 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>48847636</t>
+          <t>20086165</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>SEBERIANO</t>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>YERNON</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>MERLY</t>
+          <t>RAQUEL</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -30075,11 +30087,11 @@
         </is>
       </c>
       <c r="F473" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>30/04/1985</t>
+          <t>21/09/1976</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -30099,7 +30111,7 @@
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>05/02/2015</t>
+          <t>27/03/2018</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -30114,22 +30126,22 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>20086273</t>
+          <t>43223633</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>SEMERI</t>
+          <t>SHABONTI</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>DORITA</t>
+          <t>LILA</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -30138,21 +30150,21 @@
         </is>
       </c>
       <c r="F474" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>26/01/1956</t>
+          <t>09/05/1982</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
@@ -30162,7 +30174,7 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>29/10/2012</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
@@ -30177,45 +30189,45 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>20086276</t>
+          <t>72603683</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>SHAVONTI</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>CHOMPATI</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>CAROLA</t>
+          <t>JACKIMER</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>09/02/1968</t>
+          <t>26/10/2001</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
@@ -30225,7 +30237,7 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>06/02/2015</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
@@ -30240,45 +30252,45 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>80430197</t>
+          <t>72603685</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>SHAVONTI</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>USIAS</t>
+          <t>NAY</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>09/01/1977</t>
+          <t>22/06/2003</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
@@ -30288,7 +30300,7 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>03/05/2024</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -30303,45 +30315,45 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>20086165</t>
+          <t>61604385</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>SHAVONTI</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>YERNON</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>RAQUEL</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>21/09/1976</t>
+          <t>28/12/2008</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
@@ -30351,7 +30363,7 @@
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>27/03/2018</t>
+          <t>11/11/2011</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
@@ -30366,45 +30378,45 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>43223633</t>
+          <t>63452741</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>SHABONTI</t>
+          <t>SHAVONTI</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>LILA</t>
+          <t>EDGAR</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>09/05/1982</t>
+          <t>03/03/2013</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
@@ -30414,7 +30426,7 @@
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>29/10/2012</t>
+          <t>06/08/2014</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
@@ -30429,7 +30441,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>72603683</t>
+          <t>80085672</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -30439,12 +30451,12 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>HASA</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>JACKIMER</t>
+          <t>PACION</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -30453,21 +30465,21 @@
         </is>
       </c>
       <c r="F479" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>26/10/2001</t>
+          <t>09/04/1976</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
@@ -30477,7 +30489,7 @@
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
@@ -30492,7 +30504,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>72603685</t>
+          <t>80085665</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -30502,35 +30514,35 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>HASA</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>NAY</t>
+          <t>IVAN</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>22/06/2003</t>
+          <t>07/09/1978</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
@@ -30540,7 +30552,7 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -30555,7 +30567,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>61604385</t>
+          <t>44590209</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -30565,12 +30577,12 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>HASA</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>PANCHO</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -30579,21 +30591,21 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>28/12/2008</t>
+          <t>09/04/1981</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
@@ -30618,7 +30630,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>63452741</t>
+          <t>60401552</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -30628,12 +30640,12 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>HIVI</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>EDGAR</t>
+          <t>EDER ROY</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -30642,16 +30654,16 @@
         </is>
       </c>
       <c r="F482" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>03/03/2013</t>
+          <t>22/07/2002</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -30666,7 +30678,7 @@
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>06/08/2014</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -30681,7 +30693,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>80085672</t>
+          <t>60401551</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -30691,35 +30703,35 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>HASA</t>
+          <t>HIVI</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>PACION</t>
+          <t>ANALIBETH</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F483" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>09/04/1976</t>
+          <t>26/03/2008</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -30744,7 +30756,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>80085665</t>
+          <t>74413369</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -30754,12 +30766,12 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>HASA</t>
+          <t>IVI</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -30768,11 +30780,11 @@
         </is>
       </c>
       <c r="F484" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>07/09/1978</t>
+          <t>08/06/1996</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -30782,7 +30794,7 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -30792,7 +30804,7 @@
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
@@ -30807,7 +30819,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>44590209</t>
+          <t>74413370</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -30817,12 +30829,12 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>HASA</t>
+          <t>IVI</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>PANCHO</t>
+          <t>LINO</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -30831,16 +30843,16 @@
         </is>
       </c>
       <c r="F485" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>09/04/1981</t>
+          <t>02/05/1998</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30855,7 +30867,7 @@
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>11/11/2011</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
@@ -30870,7 +30882,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>60401552</t>
+          <t>62000372</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -30880,25 +30892,25 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>HIVI</t>
+          <t>IVI</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>EDER ROY</t>
+          <t>LESLI PILAR</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F486" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>22/07/2002</t>
+          <t>22/08/2003</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -30908,7 +30920,7 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
@@ -30933,7 +30945,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>60401551</t>
+          <t>74805409</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -30943,25 +30955,25 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>HIVI</t>
+          <t>IVI</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>ANALIBETH</t>
+          <t>CARLOS TARCICIO</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F487" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>26/03/2008</t>
+          <t>02/01/2006</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -30996,7 +31008,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>74413369</t>
+          <t>72575135</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -31006,12 +31018,12 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>IVI</t>
+          <t>QUENTIMARI</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t>HIMER</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -31020,21 +31032,21 @@
         </is>
       </c>
       <c r="F488" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>08/06/1996</t>
+          <t>30/12/2000</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
@@ -31044,7 +31056,7 @@
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
@@ -31059,7 +31071,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>74413370</t>
+          <t>60289798</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -31069,12 +31081,12 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>IVI</t>
+          <t>QUENTIMARI</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>LINO</t>
+          <t>WALTER WALDIR</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -31083,11 +31095,11 @@
         </is>
       </c>
       <c r="F489" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>02/05/1998</t>
+          <t>25/03/2007</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -31097,7 +31109,7 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
@@ -31107,7 +31119,7 @@
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -31122,7 +31134,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>62000372</t>
+          <t>63452719</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -31132,12 +31144,12 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>IVI</t>
+          <t>QUENTIMARI</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>LESLI PILAR</t>
+          <t>ZANDY XIOMARA</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -31146,21 +31158,21 @@
         </is>
       </c>
       <c r="F490" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>22/08/2003</t>
+          <t>13/06/2012</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
@@ -31170,7 +31182,7 @@
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>07/05/2014</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
@@ -31185,22 +31197,22 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>74805409</t>
+          <t>60401479</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>SHAVONTI</t>
+          <t>SHINA</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>IVI</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>CARLOS TARCICIO</t>
+          <t>YIMI ERNESTO</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -31209,11 +31221,11 @@
         </is>
       </c>
       <c r="F491" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>02/01/2006</t>
+          <t>03/11/2003</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -31233,7 +31245,7 @@
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>29/10/2012</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
@@ -31248,40 +31260,40 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>72575135</t>
+          <t>62184617</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>SHAVONTI</t>
+          <t>SHINA</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>QUENTIMARI</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>HIMER</t>
+          <t>ROCIO DEL PILAR</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>30/12/2000</t>
+          <t>02/04/2009</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -31296,7 +31308,7 @@
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>29/10/2012</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -31311,22 +31323,22 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>60289798</t>
+          <t>81808123</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>SHAVONTI</t>
+          <t>SHINA</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>QUENTIMARI</t>
+          <t>CHUÑO</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>WALTER WALDIR</t>
+          <t>GILBERTO GABRIEL</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -31335,21 +31347,21 @@
         </is>
       </c>
       <c r="F493" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>25/03/2007</t>
+          <t>28/03/2018</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
@@ -31359,7 +31371,7 @@
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>28/03/2023</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -31374,45 +31386,45 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>63452719</t>
+          <t>80421441</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>SHAVONTI</t>
+          <t>SITICONANTSI</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>QUENTIMARI</t>
+          <t>AMPATI</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>ZANDY XIOMARA</t>
+          <t>LEONARDO</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>13/06/2012</t>
+          <t>02/01/1979</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
@@ -31422,7 +31434,7 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>07/05/2014</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -31437,40 +31449,40 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>62184617</t>
+          <t>60103167</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>SHINA</t>
+          <t>SITICONANTSI</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>ROCIO DEL PILAR</t>
+          <t>YONER</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>02/04/2009</t>
+          <t>06/12/2000</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -31485,7 +31497,7 @@
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>29/10/2012</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -31500,22 +31512,22 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>81808123</t>
+          <t>60103168</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>SHINA</t>
+          <t>SITICONANTSI</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>GILBERTO GABRIEL</t>
+          <t>FRAY RIBALDO</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -31524,84 +31536,80 @@
         </is>
       </c>
       <c r="F496" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>28/03/2018</t>
+          <t>21/01/2006</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
         <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>19/12/2012</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M496" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr"/>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>SITICONANTSI</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>ROSALES</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F497" t="n">
+        <v>1</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>15/03/2025</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I496" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J496" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K496" t="inlineStr">
-        <is>
-          <t>28/03/2023</t>
-        </is>
-      </c>
-      <c r="L496" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M496" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>80421441</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>SITICONANTSI</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>AMPATI</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>LEONARDO</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F497" t="n">
-        <v>47</v>
-      </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>02/01/1979</t>
-        </is>
-      </c>
-      <c r="H497" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
@@ -31611,7 +31619,7 @@
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>15/03/2025</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -31626,22 +31634,22 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>60103167</t>
+          <t>20086239</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>SITICONANTSI</t>
+          <t>SITICONATZI</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>AMPATI</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>YONER</t>
+          <t>CHAPIAMA</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -31650,21 +31658,21 @@
         </is>
       </c>
       <c r="F498" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>06/12/2000</t>
+          <t>01/01/1972</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
@@ -31689,12 +31697,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>60103168</t>
+          <t>82369302</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>SITICONANTSI</t>
+          <t>SITICONATZI</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -31704,30 +31712,30 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>FRAY RIBALDO</t>
+          <t>YUNET YULEISI</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>21/01/2006</t>
+          <t>13/09/2023</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
@@ -31737,7 +31745,7 @@
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>24/05/2024</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
@@ -31750,20 +31758,24 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr"/>
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>48099744</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>SITICONANTSI</t>
+          <t>SITICONATZI</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>YULI</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -31772,21 +31784,21 @@
         </is>
       </c>
       <c r="F500" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>15/03/2025</t>
+          <t>12/07/1993</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
@@ -31796,7 +31808,7 @@
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>15/03/2025</t>
+          <t>29/05/2020</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -31811,7 +31823,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>20086239</t>
+          <t>60401472</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -31821,30 +31833,30 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>AMPATI</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>CHAPIAMA</t>
+          <t>LIZBETH</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>01/01/1972</t>
+          <t>29/01/1998</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31859,7 +31871,7 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -31874,7 +31886,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>82369302</t>
+          <t>74805383</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -31884,35 +31896,35 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>CAMAITERI</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>YUNET YULEISI</t>
+          <t>CLEVER</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>13/09/2023</t>
+          <t>30/06/2003</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
@@ -31922,7 +31934,7 @@
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>24/05/2024</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
@@ -31937,7 +31949,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>48099744</t>
+          <t>60401486</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -31952,7 +31964,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>YULI</t>
+          <t>MIRIAN GLADIS</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -31961,21 +31973,21 @@
         </is>
       </c>
       <c r="F503" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>12/07/1993</t>
+          <t>09/08/2008</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
@@ -31985,7 +31997,7 @@
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>29/05/2020</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
@@ -32000,7 +32012,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>60401472</t>
+          <t>60401485</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -32015,20 +32027,20 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>LIZBETH</t>
+          <t>LLEISON CHAPIAMA</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>29/01/1998</t>
+          <t>09/08/2008</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -32038,7 +32050,7 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
@@ -32063,45 +32075,45 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>74805383</t>
+          <t>20086262</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>SITICONATZI</t>
+          <t>SITIKONANTZI</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>CLEVER</t>
+          <t>TANIA</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>30/06/2003</t>
+          <t>04/01/1962</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
@@ -32111,7 +32123,7 @@
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>14/11/2011</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -32126,45 +32138,45 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>60401486</t>
+          <t>80085661</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>SITICONATZI</t>
+          <t>SITIKONANTZI</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>KENTIMARI</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>MIRIAN GLADIS</t>
+          <t>LUCIANO</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F506" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>09/08/2008</t>
+          <t>21/07/1974</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
@@ -32189,22 +32201,22 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>60401485</t>
+          <t>74773340</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>SITICONATZI</t>
+          <t>SITIKONANTZI</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>CAMAITERI</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>LLEISON CHAPIAMA</t>
+          <t>EULOGIO</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -32213,11 +32225,11 @@
         </is>
       </c>
       <c r="F507" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>09/08/2008</t>
+          <t>04/09/1998</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -32227,7 +32239,7 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
@@ -32252,7 +32264,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>20086262</t>
+          <t>74771581</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -32262,12 +32274,12 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>TANIA</t>
+          <t>BERTI LUZ SENAIDA</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -32276,21 +32288,21 @@
         </is>
       </c>
       <c r="F508" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>04/01/1962</t>
+          <t>30/09/2000</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
@@ -32300,7 +32312,7 @@
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>14/11/2011</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -32315,7 +32327,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>80085661</t>
+          <t>74773339</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -32325,12 +32337,12 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>KENTIMARI</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>LUCIANO</t>
+          <t>LUIS JHANS</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -32339,21 +32351,21 @@
         </is>
       </c>
       <c r="F509" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>21/07/1974</t>
+          <t>22/06/2003</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
@@ -32363,7 +32375,7 @@
       </c>
       <c r="K509" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>19/12/2012</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
@@ -32378,7 +32390,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>74773340</t>
+          <t>63255882</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -32393,20 +32405,20 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>EULOGIO</t>
+          <t>LIZ ANI</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F510" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>04/09/1998</t>
+          <t>13/12/2005</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -32416,7 +32428,7 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
@@ -32441,7 +32453,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>74771581</t>
+          <t>63255883</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -32456,20 +32468,20 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>BERTI LUZ SENAIDA</t>
+          <t>MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>30/09/2000</t>
+          <t>28/01/2008</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -32504,7 +32516,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>74773339</t>
+          <t>62690584</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -32519,7 +32531,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>LUIS JHANS</t>
+          <t>ULIVER RAUL</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -32528,21 +32540,21 @@
         </is>
       </c>
       <c r="F512" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>22/06/2003</t>
+          <t>22/03/2012</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
@@ -32552,7 +32564,7 @@
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>19/12/2012</t>
+          <t>09/06/2015</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
@@ -32567,7 +32579,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>63255882</t>
+          <t>81183715</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -32582,30 +32594,30 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>LIZ ANI</t>
+          <t>JHAN JAIRO LUCIANO</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F513" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>13/12/2005</t>
+          <t>25/02/2016</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
@@ -32615,7 +32627,7 @@
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>18/05/2021</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -32630,22 +32642,22 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>63255883</t>
+          <t>47932472</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>SITIKONANTZI</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>MARCOS ANTONIO</t>
+          <t>JHONATAN</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -32654,21 +32666,21 @@
         </is>
       </c>
       <c r="F514" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>28/01/2008</t>
+          <t>20/09/1993</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
@@ -32678,7 +32690,7 @@
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>06/04/2015</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
@@ -32693,45 +32705,45 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>62690584</t>
+          <t>94321235</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>SITIKONANTZI</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>ULIVER RAUL</t>
+          <t>JAZMIN CATALEYA</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F515" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>22/03/2012</t>
+          <t>20/07/2025</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
@@ -32741,7 +32753,7 @@
       </c>
       <c r="K515" t="inlineStr">
         <is>
-          <t>09/06/2015</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
@@ -32756,22 +32768,22 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>81183715</t>
+          <t>77246048</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>SITIKONANTZI</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>JHAN JAIRO LUCIANO</t>
+          <t>EDWIN</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -32780,21 +32792,21 @@
         </is>
       </c>
       <c r="F516" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>25/02/2016</t>
+          <t>29/11/1996</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
@@ -32804,7 +32816,7 @@
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t>18/05/2021</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
@@ -32819,22 +32831,22 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>47932472</t>
+          <t>94193727</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>CARRION</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>JHONATAN</t>
+          <t>HANIEL HEFER</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -32843,21 +32855,21 @@
         </is>
       </c>
       <c r="F517" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>20/09/1993</t>
+          <t>23/03/2025</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
@@ -32867,7 +32879,7 @@
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>06/04/2015</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
@@ -32880,37 +32892,33 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>94321235</t>
-        </is>
-      </c>
+      <c r="A518" t="inlineStr"/>
       <c r="B518" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>MASHICOLI</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>JAZMIN CATALEYA</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F518" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>20/07/2025</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -32930,7 +32938,7 @@
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
@@ -32945,27 +32953,27 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>77246048</t>
+          <t>49091621</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>TORREZ</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>EDWIN</t>
+          <t>MAGDALENA</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F519" t="n">
@@ -32973,7 +32981,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>29/11/1996</t>
+          <t>05/09/1996</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -32983,7 +32991,7 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
@@ -32993,7 +33001,7 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -33008,22 +33016,22 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>94193727</t>
+          <t>63452821</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TUANAMA</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>CARRION</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>HANIEL HEFER</t>
+          <t>FHUSTO PASTOR</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -33032,82 +33040,86 @@
         </is>
       </c>
       <c r="F520" t="n">
+        <v>10</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>06/04/2016</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>18/05/2021</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>RIO TAMBO</t>
+        </is>
+      </c>
+      <c r="M520" t="n">
+        <v>120608</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>82164071</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>UGARTE</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>ARIAS</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>NAYTI CLISMETH</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F521" t="n">
         <v>1</v>
       </c>
-      <c r="G520" t="inlineStr">
-        <is>
-          <t>23/03/2025</t>
-        </is>
-      </c>
-      <c r="H520" t="inlineStr">
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
         <is>
           <t>1.NIÑO</t>
         </is>
       </c>
-      <c r="I520" t="inlineStr">
+      <c r="I521" t="inlineStr">
         <is>
           <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
-      <c r="J520" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K520" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="L520" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M520" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr"/>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>TORRES</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>MASHICOLI</t>
-        </is>
-      </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="E521" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F521" t="n">
-        <v>0</v>
-      </c>
-      <c r="G521" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="H521" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I521" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
       <c r="J521" t="inlineStr">
         <is>
           <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
@@ -33115,7 +33127,7 @@
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -33130,22 +33142,22 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>49091621</t>
+          <t>91007272</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>TORREZ</t>
+          <t>URQUIA</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>SITICONATZI</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>MAGDALENA</t>
+          <t>MIA BETSABE</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -33154,21 +33166,21 @@
         </is>
       </c>
       <c r="F522" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>05/09/1996</t>
+          <t>14/10/2018</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
@@ -33178,7 +33190,7 @@
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>14/10/2023</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -33193,22 +33205,22 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>63452821</t>
+          <t>94353375</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>TUANAMA</t>
+          <t>URQUIA</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>SITICONATZI</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>FHUSTO PASTOR</t>
+          <t>ANGEL GABRIEL</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -33217,11 +33229,11 @@
         </is>
       </c>
       <c r="F523" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>06/04/2016</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -33231,7 +33243,7 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
@@ -33241,7 +33253,7 @@
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>18/05/2021</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
@@ -33254,24 +33266,20 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>82164071</t>
-        </is>
-      </c>
+      <c r="A524" t="inlineStr"/>
       <c r="B524" t="inlineStr">
         <is>
-          <t>UGARTE</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>MIERIANO</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>NAYTI CLISMETH</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -33280,11 +33288,11 @@
         </is>
       </c>
       <c r="F524" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>22/05/2024</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -33304,7 +33312,7 @@
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>22/05/2024</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
@@ -33319,22 +33327,22 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>91007272</t>
+          <t>94428874</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>URQUIA</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>SITICONATZI</t>
+          <t>SAMUEL</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>MIA BETSABE</t>
+          <t>LUZ NATALY MEYLI</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -33343,11 +33351,11 @@
         </is>
       </c>
       <c r="F525" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>14/10/2018</t>
+          <t>21/10/2025</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -33357,7 +33365,7 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
@@ -33367,7 +33375,7 @@
       </c>
       <c r="K525" t="inlineStr">
         <is>
-          <t>14/10/2023</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
@@ -33382,22 +33390,22 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>94353375</t>
+          <t>81992660</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>URQUIA</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>SITICONATZI</t>
+          <t>AVENCHARI</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>ANGEL GABRIEL</t>
+          <t>DEYSER ESNAYDER</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -33406,11 +33414,11 @@
         </is>
       </c>
       <c r="F526" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>14/08/2025</t>
+          <t>15/10/2021</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -33430,7 +33438,7 @@
       </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>06/01/2023</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
@@ -33445,40 +33453,40 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>46282309</t>
+          <t>82000182</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>VALDERRAMA</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>CHUÑO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>GUILLERMO</t>
+          <t>GISANIA</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F527" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>26/12/1989</t>
+          <t>11/12/2018</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -33493,7 +33501,7 @@
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -33506,20 +33514,24 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="inlineStr"/>
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>61604387</t>
+        </is>
+      </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>ZABALETA</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>MIERIANO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>JHASMIN GUISELLA</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -33528,21 +33540,21 @@
         </is>
       </c>
       <c r="F528" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>22/05/2024</t>
+          <t>10/06/2003</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
@@ -33552,7 +33564,7 @@
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>22/05/2024</t>
+          <t>20/12/2012</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -33567,35 +33579,35 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>94428874</t>
+          <t>81899399</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>ZANDOVAL</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>SAMUEL</t>
+          <t>CHUBIAVANTI</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>LUZ NATALY MEYLI</t>
+          <t>ANDERSON</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F529" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>21/10/2025</t>
+          <t>17/06/2021</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -33605,7 +33617,7 @@
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
@@ -33615,7 +33627,7 @@
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
@@ -33630,35 +33642,35 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>81992660</t>
+          <t>94018964</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>ZANDOVAL</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>AVENCHARI</t>
+          <t>CHUBIAVANTI</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>DEYSER ESNAYDER</t>
+          <t>ELIZABET</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F530" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
+          <t>17/10/2024</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -33678,7 +33690,7 @@
       </c>
       <c r="K530" t="inlineStr">
         <is>
-          <t>06/01/2023</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
@@ -33693,22 +33705,22 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>82000182</t>
+          <t>82206035</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>ZEBASTIAN</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>GISANIA</t>
+          <t>MILAGROS</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -33717,11 +33729,11 @@
         </is>
       </c>
       <c r="F531" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>11/12/2018</t>
+          <t>25/12/2025</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -33731,7 +33743,7 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
@@ -33741,7 +33753,7 @@
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
@@ -33756,45 +33768,45 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>61604387</t>
+          <t>93047747</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>ZABALETA</t>
+          <t>ZUCA</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>JHASMIN GUISELLA</t>
+          <t>ANTHONY</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F532" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>10/06/2003</t>
+          <t>05/09/2022</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
@@ -33804,7 +33816,7 @@
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>20/12/2012</t>
+          <t>19/03/2024</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -33819,45 +33831,45 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>81899399</t>
+          <t>62000445</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>ZANDOVAL</t>
+          <t>ÑACO</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>CHUBIAVANTI</t>
+          <t>SEBERIANO</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>ANDERSON</t>
+          <t>SUSANA</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F533" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>17/06/2021</t>
+          <t>14/10/2000</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
@@ -33867,7 +33879,7 @@
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>05/02/2015</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -33882,45 +33894,45 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>94018964</t>
+          <t>62000432</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>ZANDOVAL</t>
+          <t>ÑACO</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>CHUBIAVANTI</t>
+          <t>SEBERIANO</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>ELIZABET</t>
+          <t>EMANUEL DANIEL</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F534" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>17/10/2024</t>
+          <t>24/12/2010</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
@@ -33930,7 +33942,7 @@
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>05/02/2015</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
@@ -33939,258 +33951,6 @@
         </is>
       </c>
       <c r="M534" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>82206035</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>ZEBASTIAN</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>PEREZ</t>
-        </is>
-      </c>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>MILAGROS</t>
-        </is>
-      </c>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F535" t="n">
-        <v>1</v>
-      </c>
-      <c r="G535" t="inlineStr">
-        <is>
-          <t>25/12/2025</t>
-        </is>
-      </c>
-      <c r="H535" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I535" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
-      <c r="J535" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K535" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="L535" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M535" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>93047747</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>ZUCA</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>NAVARRO</t>
-        </is>
-      </c>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>ANTHONY</t>
-        </is>
-      </c>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F536" t="n">
-        <v>4</v>
-      </c>
-      <c r="G536" t="inlineStr">
-        <is>
-          <t>05/09/2022</t>
-        </is>
-      </c>
-      <c r="H536" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I536" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
-      <c r="J536" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K536" t="inlineStr">
-        <is>
-          <t>19/03/2024</t>
-        </is>
-      </c>
-      <c r="L536" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M536" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>62000445</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>ÑACO</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>SEBERIANO</t>
-        </is>
-      </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>SUSANA</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F537" t="n">
-        <v>26</v>
-      </c>
-      <c r="G537" t="inlineStr">
-        <is>
-          <t>14/10/2000</t>
-        </is>
-      </c>
-      <c r="H537" t="inlineStr">
-        <is>
-          <t>3.JOVEN</t>
-        </is>
-      </c>
-      <c r="I537" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J537" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K537" t="inlineStr">
-        <is>
-          <t>05/02/2015</t>
-        </is>
-      </c>
-      <c r="L537" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M537" t="n">
-        <v>120608</v>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>62000432</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>ÑACO</t>
-        </is>
-      </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>SEBERIANO</t>
-        </is>
-      </c>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>EMANUEL DANIEL</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F538" t="n">
-        <v>16</v>
-      </c>
-      <c r="G538" t="inlineStr">
-        <is>
-          <t>24/12/2010</t>
-        </is>
-      </c>
-      <c r="H538" t="inlineStr">
-        <is>
-          <t>2.ADOLESCENTE</t>
-        </is>
-      </c>
-      <c r="I538" t="inlineStr">
-        <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
-        </is>
-      </c>
-      <c r="J538" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K538" t="inlineStr">
-        <is>
-          <t>05/02/2015</t>
-        </is>
-      </c>
-      <c r="L538" t="inlineStr">
-        <is>
-          <t>RIO TAMBO</t>
-        </is>
-      </c>
-      <c r="M538" t="n">
         <v>120608</v>
       </c>
     </row>
